--- a/artfynd/S 1898-2025 artfynd.xlsx
+++ b/artfynd/S 1898-2025 artfynd.xlsx
@@ -1638,7 +1638,7 @@
         <v>127009893</v>
       </c>
       <c r="B11" t="n">
-        <v>89354</v>
+        <v>89474</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="AE11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">

--- a/artfynd/S 1898-2025 artfynd.xlsx
+++ b/artfynd/S 1898-2025 artfynd.xlsx
@@ -1638,7 +1638,7 @@
         <v>127009893</v>
       </c>
       <c r="B11" t="n">
-        <v>89474</v>
+        <v>89476</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/S 1898-2025 artfynd.xlsx
+++ b/artfynd/S 1898-2025 artfynd.xlsx
@@ -1638,7 +1638,7 @@
         <v>127009893</v>
       </c>
       <c r="B11" t="n">
-        <v>89476</v>
+        <v>89478</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/S 1898-2025 artfynd.xlsx
+++ b/artfynd/S 1898-2025 artfynd.xlsx
@@ -1638,7 +1638,7 @@
         <v>127009893</v>
       </c>
       <c r="B11" t="n">
-        <v>89478</v>
+        <v>89479</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/S 1898-2025 artfynd.xlsx
+++ b/artfynd/S 1898-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ383"/>
+  <dimension ref="A1:AZ384"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34957,10 +34957,10 @@
     </row>
     <row r="299">
       <c r="A299" t="n">
-        <v>109574015</v>
+        <v>137124272</v>
       </c>
       <c r="B299" t="n">
-        <v>4775</v>
+        <v>57195</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -34968,40 +34968,42 @@
         </is>
       </c>
       <c r="E299" t="n">
-        <v>100299</v>
+        <v>100138</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
-        </is>
-      </c>
-      <c r="I299" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I299" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K299" t="inlineStr"/>
-      <c r="M299" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+      <c r="L299" t="inlineStr"/>
+      <c r="M299" t="inlineStr"/>
+      <c r="N299" t="inlineStr"/>
       <c r="P299" t="inlineStr">
         <is>
-          <t>Stor-Moberg, Dlr</t>
+          <t>Stor Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q299" t="n">
-        <v>511519</v>
+        <v>511584</v>
       </c>
       <c r="R299" t="n">
-        <v>6733203</v>
+        <v>6733481</v>
       </c>
       <c r="S299" t="n">
         <v>25</v>
@@ -35028,22 +35030,27 @@
       </c>
       <c r="Y299" t="inlineStr">
         <is>
-          <t>2023-05-28</t>
+          <t>2024-02-05</t>
         </is>
       </c>
       <c r="Z299" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA299" t="inlineStr">
         <is>
-          <t>2023-05-28</t>
+          <t>2024-02-05</t>
         </is>
       </c>
       <c r="AB299" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>11:38</t>
+        </is>
+      </c>
+      <c r="AC299" t="inlineStr">
+        <is>
+          <t>Färska tjäderspår i nysnö.</t>
         </is>
       </c>
       <c r="AD299" t="b">
@@ -35058,24 +35065,24 @@
       <c r="AT299" t="inlineStr"/>
       <c r="AW299" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX299" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY299" t="inlineStr"/>
       <c r="AZ299" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/109574015</t>
+          <t>https://artportalen.se/Sighting/137124272</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="n">
-        <v>109579875</v>
+        <v>109574015</v>
       </c>
       <c r="B300" t="n">
         <v>4775</v>
@@ -35112,14 +35119,14 @@
       </c>
       <c r="P300" t="inlineStr">
         <is>
-          <t>Grim-Moberg, Dlr</t>
+          <t>Stor-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q300" t="n">
-        <v>511267</v>
+        <v>511519</v>
       </c>
       <c r="R300" t="n">
-        <v>6733219</v>
+        <v>6733203</v>
       </c>
       <c r="S300" t="n">
         <v>25</v>
@@ -35151,7 +35158,7 @@
       </c>
       <c r="Z300" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="AA300" t="inlineStr">
@@ -35161,7 +35168,7 @@
       </c>
       <c r="AB300" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="AD300" t="b">
@@ -35187,13 +35194,13 @@
       <c r="AY300" t="inlineStr"/>
       <c r="AZ300" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/109579875</t>
+          <t>https://artportalen.se/Sighting/109574015</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="n">
-        <v>127033454</v>
+        <v>109579875</v>
       </c>
       <c r="B301" t="n">
         <v>4775</v>
@@ -35222,6 +35229,7 @@
         </is>
       </c>
       <c r="I301" t="inlineStr"/>
+      <c r="K301" t="inlineStr"/>
       <c r="M301" t="inlineStr">
         <is>
           <t>färska gnagspår</t>
@@ -35229,17 +35237,17 @@
       </c>
       <c r="P301" t="inlineStr">
         <is>
-          <t>Grim-Moberg, Grim-Moberg, Dlr</t>
+          <t>Grim-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q301" t="n">
-        <v>511393</v>
+        <v>511267</v>
       </c>
       <c r="R301" t="n">
-        <v>6733148</v>
+        <v>6733219</v>
       </c>
       <c r="S301" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="T301" t="inlineStr">
         <is>
@@ -35263,22 +35271,22 @@
       </c>
       <c r="Y301" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2023-05-28</t>
         </is>
       </c>
       <c r="Z301" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA301" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2023-05-28</t>
         </is>
       </c>
       <c r="AB301" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD301" t="b">
@@ -35304,13 +35312,13 @@
       <c r="AY301" t="inlineStr"/>
       <c r="AZ301" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127033454</t>
+          <t>https://artportalen.se/Sighting/109579875</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="n">
-        <v>127047724</v>
+        <v>127033454</v>
       </c>
       <c r="B302" t="n">
         <v>4775</v>
@@ -35339,28 +35347,24 @@
         </is>
       </c>
       <c r="I302" t="inlineStr"/>
-      <c r="J302" t="inlineStr"/>
-      <c r="K302" t="inlineStr"/>
-      <c r="L302" t="inlineStr"/>
       <c r="M302" t="inlineStr">
         <is>
           <t>färska gnagspår</t>
         </is>
       </c>
-      <c r="N302" t="inlineStr"/>
       <c r="P302" t="inlineStr">
         <is>
-          <t>Fjällgrycksbo, Dlr</t>
+          <t>Grim-Moberg, Grim-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q302" t="n">
-        <v>511260</v>
+        <v>511393</v>
       </c>
       <c r="R302" t="n">
-        <v>6733233</v>
+        <v>6733148</v>
       </c>
       <c r="S302" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T302" t="inlineStr">
         <is>
@@ -35389,7 +35393,7 @@
       </c>
       <c r="Z302" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AA302" t="inlineStr">
@@ -35399,7 +35403,7 @@
       </c>
       <c r="AB302" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AD302" t="b">
@@ -35408,7 +35412,6 @@
       <c r="AE302" t="b">
         <v>0</v>
       </c>
-      <c r="AF302" t="inlineStr"/>
       <c r="AG302" t="b">
         <v>0</v>
       </c>
@@ -35426,13 +35429,13 @@
       <c r="AY302" t="inlineStr"/>
       <c r="AZ302" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127047724</t>
+          <t>https://artportalen.se/Sighting/127033454</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="n">
-        <v>127047835</v>
+        <v>127047724</v>
       </c>
       <c r="B303" t="n">
         <v>4775</v>
@@ -35466,7 +35469,7 @@
       <c r="L303" t="inlineStr"/>
       <c r="M303" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N303" t="inlineStr"/>
@@ -35476,10 +35479,10 @@
         </is>
       </c>
       <c r="Q303" t="n">
-        <v>511199</v>
+        <v>511260</v>
       </c>
       <c r="R303" t="n">
-        <v>6733259</v>
+        <v>6733233</v>
       </c>
       <c r="S303" t="n">
         <v>10</v>
@@ -35511,7 +35514,7 @@
       </c>
       <c r="Z303" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AA303" t="inlineStr">
@@ -35521,7 +35524,7 @@
       </c>
       <c r="AB303" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AD303" t="b">
@@ -35548,13 +35551,13 @@
       <c r="AY303" t="inlineStr"/>
       <c r="AZ303" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127047835</t>
+          <t>https://artportalen.se/Sighting/127047724</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="n">
-        <v>127048049</v>
+        <v>127047835</v>
       </c>
       <c r="B304" t="n">
         <v>4775</v>
@@ -35588,7 +35591,7 @@
       <c r="L304" t="inlineStr"/>
       <c r="M304" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N304" t="inlineStr"/>
@@ -35598,10 +35601,10 @@
         </is>
       </c>
       <c r="Q304" t="n">
-        <v>511187</v>
+        <v>511199</v>
       </c>
       <c r="R304" t="n">
-        <v>6733200</v>
+        <v>6733259</v>
       </c>
       <c r="S304" t="n">
         <v>10</v>
@@ -35633,7 +35636,7 @@
       </c>
       <c r="Z304" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA304" t="inlineStr">
@@ -35643,7 +35646,7 @@
       </c>
       <c r="AB304" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD304" t="b">
@@ -35670,13 +35673,13 @@
       <c r="AY304" t="inlineStr"/>
       <c r="AZ304" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127048049</t>
+          <t>https://artportalen.se/Sighting/127047835</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="n">
-        <v>127048206</v>
+        <v>127048049</v>
       </c>
       <c r="B305" t="n">
         <v>4775</v>
@@ -35716,14 +35719,14 @@
       <c r="N305" t="inlineStr"/>
       <c r="P305" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Fjällgrycksbo, Dlr</t>
         </is>
       </c>
       <c r="Q305" t="n">
-        <v>511253</v>
+        <v>511187</v>
       </c>
       <c r="R305" t="n">
-        <v>6733209</v>
+        <v>6733200</v>
       </c>
       <c r="S305" t="n">
         <v>10</v>
@@ -35755,7 +35758,7 @@
       </c>
       <c r="Z305" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA305" t="inlineStr">
@@ -35765,7 +35768,7 @@
       </c>
       <c r="AB305" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AD305" t="b">
@@ -35792,13 +35795,13 @@
       <c r="AY305" t="inlineStr"/>
       <c r="AZ305" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127048206</t>
+          <t>https://artportalen.se/Sighting/127048049</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="n">
-        <v>127085165</v>
+        <v>127048206</v>
       </c>
       <c r="B306" t="n">
         <v>4775</v>
@@ -35827,21 +35830,25 @@
         </is>
       </c>
       <c r="I306" t="inlineStr"/>
+      <c r="J306" t="inlineStr"/>
+      <c r="K306" t="inlineStr"/>
+      <c r="L306" t="inlineStr"/>
       <c r="M306" t="inlineStr">
         <is>
           <t>färska gnagspår</t>
         </is>
       </c>
+      <c r="N306" t="inlineStr"/>
       <c r="P306" t="inlineStr">
         <is>
-          <t>Stor-Moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q306" t="n">
-        <v>511678</v>
+        <v>511253</v>
       </c>
       <c r="R306" t="n">
-        <v>6733602</v>
+        <v>6733209</v>
       </c>
       <c r="S306" t="n">
         <v>10</v>
@@ -35868,12 +35875,22 @@
       </c>
       <c r="Y306" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="Z306" t="inlineStr">
+        <is>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA306" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AB306" t="inlineStr">
+        <is>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD306" t="b">
@@ -35882,30 +35899,31 @@
       <c r="AE306" t="b">
         <v>0</v>
       </c>
+      <c r="AF306" t="inlineStr"/>
       <c r="AG306" t="b">
         <v>0</v>
       </c>
       <c r="AT306" t="inlineStr"/>
       <c r="AW306" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX306" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY306" t="inlineStr"/>
       <c r="AZ306" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127085165</t>
+          <t>https://artportalen.se/Sighting/127048206</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="n">
-        <v>127085166</v>
+        <v>127085165</v>
       </c>
       <c r="B307" t="n">
         <v>4775</v>
@@ -35941,14 +35959,14 @@
       </c>
       <c r="P307" t="inlineStr">
         <is>
-          <t>Grim-Moberg, Dlr</t>
+          <t>Stor-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q307" t="n">
-        <v>511354</v>
+        <v>511678</v>
       </c>
       <c r="R307" t="n">
-        <v>6733445</v>
+        <v>6733602</v>
       </c>
       <c r="S307" t="n">
         <v>10</v>
@@ -36006,13 +36024,13 @@
       <c r="AY307" t="inlineStr"/>
       <c r="AZ307" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127085166</t>
+          <t>https://artportalen.se/Sighting/127085165</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="n">
-        <v>127085167</v>
+        <v>127085166</v>
       </c>
       <c r="B308" t="n">
         <v>4775</v>
@@ -36052,10 +36070,10 @@
         </is>
       </c>
       <c r="Q308" t="n">
-        <v>511302</v>
+        <v>511354</v>
       </c>
       <c r="R308" t="n">
-        <v>6733258</v>
+        <v>6733445</v>
       </c>
       <c r="S308" t="n">
         <v>10</v>
@@ -36113,13 +36131,13 @@
       <c r="AY308" t="inlineStr"/>
       <c r="AZ308" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127085167</t>
+          <t>https://artportalen.se/Sighting/127085166</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="n">
-        <v>127151243</v>
+        <v>127085167</v>
       </c>
       <c r="B309" t="n">
         <v>4775</v>
@@ -36155,17 +36173,17 @@
       </c>
       <c r="P309" t="inlineStr">
         <is>
-          <t>Sjös-Moberg, Sjös-Moberg, Dlr</t>
+          <t>Grim-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q309" t="n">
-        <v>511569</v>
+        <v>511302</v>
       </c>
       <c r="R309" t="n">
-        <v>6733170</v>
+        <v>6733258</v>
       </c>
       <c r="S309" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T309" t="inlineStr">
         <is>
@@ -36189,22 +36207,12 @@
       </c>
       <c r="Y309" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
-        </is>
-      </c>
-      <c r="Z309" t="inlineStr">
-        <is>
-          <t>12:44</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="AA309" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
-        </is>
-      </c>
-      <c r="AB309" t="inlineStr">
-        <is>
-          <t>12:44</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="AD309" t="b">
@@ -36219,24 +36227,24 @@
       <c r="AT309" t="inlineStr"/>
       <c r="AW309" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX309" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY309" t="inlineStr"/>
       <c r="AZ309" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127151243</t>
+          <t>https://artportalen.se/Sighting/127085167</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="n">
-        <v>127154189</v>
+        <v>127151243</v>
       </c>
       <c r="B310" t="n">
         <v>4775</v>
@@ -36267,19 +36275,19 @@
       <c r="I310" t="inlineStr"/>
       <c r="M310" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P310" t="inlineStr">
         <is>
-          <t>Moberg, Moberg, Dlr</t>
+          <t>Sjös-Moberg, Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q310" t="n">
-        <v>511727</v>
+        <v>511569</v>
       </c>
       <c r="R310" t="n">
-        <v>6733247</v>
+        <v>6733170</v>
       </c>
       <c r="S310" t="n">
         <v>9</v>
@@ -36311,7 +36319,7 @@
       </c>
       <c r="Z310" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA310" t="inlineStr">
@@ -36321,7 +36329,7 @@
       </c>
       <c r="AB310" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD310" t="b">
@@ -36347,13 +36355,13 @@
       <c r="AY310" t="inlineStr"/>
       <c r="AZ310" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127154189</t>
+          <t>https://artportalen.se/Sighting/127151243</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="n">
-        <v>127158677</v>
+        <v>127154189</v>
       </c>
       <c r="B311" t="n">
         <v>4775</v>
@@ -36382,28 +36390,24 @@
         </is>
       </c>
       <c r="I311" t="inlineStr"/>
-      <c r="J311" t="inlineStr"/>
-      <c r="K311" t="inlineStr"/>
-      <c r="L311" t="inlineStr"/>
       <c r="M311" t="inlineStr">
         <is>
           <t>äldre gnagspår</t>
         </is>
       </c>
-      <c r="N311" t="inlineStr"/>
       <c r="P311" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Moberg, Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q311" t="n">
-        <v>511347</v>
+        <v>511727</v>
       </c>
       <c r="R311" t="n">
-        <v>6733129</v>
+        <v>6733247</v>
       </c>
       <c r="S311" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T311" t="inlineStr">
         <is>
@@ -36432,7 +36436,7 @@
       </c>
       <c r="Z311" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA311" t="inlineStr">
@@ -36442,7 +36446,7 @@
       </c>
       <c r="AB311" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD311" t="b">
@@ -36451,7 +36455,6 @@
       <c r="AE311" t="b">
         <v>0</v>
       </c>
-      <c r="AF311" t="inlineStr"/>
       <c r="AG311" t="b">
         <v>0</v>
       </c>
@@ -36469,13 +36472,13 @@
       <c r="AY311" t="inlineStr"/>
       <c r="AZ311" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127158677</t>
+          <t>https://artportalen.se/Sighting/127154189</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="n">
-        <v>127784884</v>
+        <v>127158677</v>
       </c>
       <c r="B312" t="n">
         <v>4775</v>
@@ -36509,20 +36512,20 @@
       <c r="L312" t="inlineStr"/>
       <c r="M312" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N312" t="inlineStr"/>
       <c r="P312" t="inlineStr">
         <is>
-          <t>Grim Moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q312" t="n">
-        <v>511474</v>
+        <v>511347</v>
       </c>
       <c r="R312" t="n">
-        <v>6733357</v>
+        <v>6733129</v>
       </c>
       <c r="S312" t="n">
         <v>10</v>
@@ -36549,12 +36552,22 @@
       </c>
       <c r="Y312" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="Z312" t="inlineStr">
+        <is>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA312" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AB312" t="inlineStr">
+        <is>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD312" t="b">
@@ -36570,27 +36583,27 @@
       <c r="AT312" t="inlineStr"/>
       <c r="AW312" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX312" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY312" t="inlineStr"/>
       <c r="AZ312" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127784884</t>
+          <t>https://artportalen.se/Sighting/127158677</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="n">
-        <v>104718188</v>
+        <v>127784884</v>
       </c>
       <c r="B313" t="n">
-        <v>5179</v>
+        <v>4775</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -36598,42 +36611,46 @@
         </is>
       </c>
       <c r="E313" t="n">
-        <v>100526</v>
+        <v>100299</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H313" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I313" t="inlineStr"/>
       <c r="J313" t="inlineStr"/>
       <c r="K313" t="inlineStr"/>
       <c r="L313" t="inlineStr"/>
-      <c r="M313" t="inlineStr"/>
+      <c r="M313" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N313" t="inlineStr"/>
       <c r="P313" t="inlineStr">
         <is>
-          <t>Leksand, Dlr</t>
+          <t>Grim Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q313" t="n">
-        <v>511448</v>
+        <v>511474</v>
       </c>
       <c r="R313" t="n">
-        <v>6733182</v>
+        <v>6733357</v>
       </c>
       <c r="S313" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T313" t="inlineStr">
         <is>
@@ -36657,22 +36674,12 @@
       </c>
       <c r="Y313" t="inlineStr">
         <is>
-          <t>2022-11-17</t>
-        </is>
-      </c>
-      <c r="Z313" t="inlineStr">
-        <is>
-          <t>12:45</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="AA313" t="inlineStr">
         <is>
-          <t>2022-11-17</t>
-        </is>
-      </c>
-      <c r="AB313" t="inlineStr">
-        <is>
-          <t>12:45</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="AD313" t="b">
@@ -36688,24 +36695,24 @@
       <c r="AT313" t="inlineStr"/>
       <c r="AW313" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX313" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY313" t="inlineStr"/>
       <c r="AZ313" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104718188</t>
+          <t>https://artportalen.se/Sighting/127784884</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="n">
-        <v>104756507</v>
+        <v>104718188</v>
       </c>
       <c r="B314" t="n">
         <v>5179</v>
@@ -36734,17 +36741,21 @@
         </is>
       </c>
       <c r="I314" t="inlineStr"/>
+      <c r="J314" t="inlineStr"/>
       <c r="K314" t="inlineStr"/>
+      <c r="L314" t="inlineStr"/>
+      <c r="M314" t="inlineStr"/>
+      <c r="N314" t="inlineStr"/>
       <c r="P314" t="inlineStr">
         <is>
           <t>Leksand, Dlr</t>
         </is>
       </c>
       <c r="Q314" t="n">
-        <v>511570</v>
+        <v>511448</v>
       </c>
       <c r="R314" t="n">
-        <v>6733177</v>
+        <v>6733182</v>
       </c>
       <c r="S314" t="n">
         <v>25</v>
@@ -36771,22 +36782,22 @@
       </c>
       <c r="Y314" t="inlineStr">
         <is>
-          <t>2022-11-20</t>
+          <t>2022-11-17</t>
         </is>
       </c>
       <c r="Z314" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA314" t="inlineStr">
         <is>
-          <t>2022-11-20</t>
+          <t>2022-11-17</t>
         </is>
       </c>
       <c r="AB314" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD314" t="b">
@@ -36795,30 +36806,31 @@
       <c r="AE314" t="b">
         <v>0</v>
       </c>
+      <c r="AF314" t="inlineStr"/>
       <c r="AG314" t="b">
         <v>0</v>
       </c>
       <c r="AT314" t="inlineStr"/>
       <c r="AW314" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX314" t="inlineStr">
         <is>
-          <t>Lisa Olson, Bo karlstens</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY314" t="inlineStr"/>
       <c r="AZ314" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104756507</t>
+          <t>https://artportalen.se/Sighting/104718188</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="n">
-        <v>106212374</v>
+        <v>104756507</v>
       </c>
       <c r="B315" t="n">
         <v>5179</v>
@@ -36850,14 +36862,14 @@
       <c r="K315" t="inlineStr"/>
       <c r="P315" t="inlineStr">
         <is>
-          <t>Stor-Moberg, Dlr</t>
+          <t>Leksand, Dlr</t>
         </is>
       </c>
       <c r="Q315" t="n">
-        <v>511343</v>
+        <v>511570</v>
       </c>
       <c r="R315" t="n">
-        <v>6733476</v>
+        <v>6733177</v>
       </c>
       <c r="S315" t="n">
         <v>25</v>
@@ -36884,22 +36896,22 @@
       </c>
       <c r="Y315" t="inlineStr">
         <is>
-          <t>2023-01-29</t>
+          <t>2022-11-20</t>
         </is>
       </c>
       <c r="Z315" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA315" t="inlineStr">
         <is>
-          <t>2023-01-29</t>
+          <t>2022-11-20</t>
         </is>
       </c>
       <c r="AB315" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD315" t="b">
@@ -36914,24 +36926,24 @@
       <c r="AT315" t="inlineStr"/>
       <c r="AW315" t="inlineStr">
         <is>
-          <t>Åke Sköld</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX315" t="inlineStr">
         <is>
-          <t>Åke Sköld</t>
+          <t>Lisa Olson, Bo karlstens</t>
         </is>
       </c>
       <c r="AY315" t="inlineStr"/>
       <c r="AZ315" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/106212374</t>
+          <t>https://artportalen.se/Sighting/104756507</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="n">
-        <v>109579783</v>
+        <v>106212374</v>
       </c>
       <c r="B316" t="n">
         <v>5179</v>
@@ -36961,21 +36973,16 @@
       </c>
       <c r="I316" t="inlineStr"/>
       <c r="K316" t="inlineStr"/>
-      <c r="M316" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P316" t="inlineStr">
         <is>
-          <t>Grim-Moberg, Dlr</t>
+          <t>Stor-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q316" t="n">
-        <v>511267</v>
+        <v>511343</v>
       </c>
       <c r="R316" t="n">
-        <v>6733219</v>
+        <v>6733476</v>
       </c>
       <c r="S316" t="n">
         <v>25</v>
@@ -37002,22 +37009,22 @@
       </c>
       <c r="Y316" t="inlineStr">
         <is>
-          <t>2023-05-28</t>
+          <t>2023-01-29</t>
         </is>
       </c>
       <c r="Z316" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA316" t="inlineStr">
         <is>
-          <t>2023-05-28</t>
+          <t>2023-01-29</t>
         </is>
       </c>
       <c r="AB316" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD316" t="b">
@@ -37032,24 +37039,24 @@
       <c r="AT316" t="inlineStr"/>
       <c r="AW316" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Åke Sköld</t>
         </is>
       </c>
       <c r="AX316" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Åke Sköld</t>
         </is>
       </c>
       <c r="AY316" t="inlineStr"/>
       <c r="AZ316" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/109579783</t>
+          <t>https://artportalen.se/Sighting/106212374</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="n">
-        <v>111765246</v>
+        <v>109579783</v>
       </c>
       <c r="B317" t="n">
         <v>5179</v>
@@ -37077,30 +37084,23 @@
           <t>Paykull, 1800</t>
         </is>
       </c>
-      <c r="I317" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J317" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
+      <c r="I317" t="inlineStr"/>
       <c r="K317" t="inlineStr"/>
-      <c r="L317" t="inlineStr"/>
-      <c r="M317" t="inlineStr"/>
-      <c r="N317" t="inlineStr"/>
+      <c r="M317" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P317" t="inlineStr">
         <is>
-          <t>Grim-Moberg, Grim-Moberg, Dlr</t>
+          <t>Grim-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q317" t="n">
-        <v>511523</v>
+        <v>511267</v>
       </c>
       <c r="R317" t="n">
-        <v>6733246</v>
+        <v>6733219</v>
       </c>
       <c r="S317" t="n">
         <v>25</v>
@@ -37127,22 +37127,22 @@
       </c>
       <c r="Y317" t="inlineStr">
         <is>
-          <t>2023-08-29</t>
+          <t>2023-05-28</t>
         </is>
       </c>
       <c r="Z317" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA317" t="inlineStr">
         <is>
-          <t>2023-08-29</t>
+          <t>2023-05-28</t>
         </is>
       </c>
       <c r="AB317" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD317" t="b">
@@ -37151,31 +37151,30 @@
       <c r="AE317" t="b">
         <v>0</v>
       </c>
-      <c r="AF317" t="inlineStr"/>
       <c r="AG317" t="b">
         <v>0</v>
       </c>
       <c r="AT317" t="inlineStr"/>
       <c r="AW317" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX317" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY317" t="inlineStr"/>
       <c r="AZ317" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111765246</t>
+          <t>https://artportalen.se/Sighting/109579783</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="n">
-        <v>115535311</v>
+        <v>111765246</v>
       </c>
       <c r="B318" t="n">
         <v>5179</v>
@@ -37203,25 +37202,33 @@
           <t>Paykull, 1800</t>
         </is>
       </c>
-      <c r="I318" t="inlineStr"/>
-      <c r="J318" t="inlineStr"/>
+      <c r="I318" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J318" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="K318" t="inlineStr"/>
       <c r="L318" t="inlineStr"/>
       <c r="M318" t="inlineStr"/>
       <c r="N318" t="inlineStr"/>
       <c r="P318" t="inlineStr">
         <is>
-          <t>Leksand, Leksand, Dlr</t>
+          <t>Grim-Moberg, Grim-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q318" t="n">
-        <v>511290</v>
+        <v>511523</v>
       </c>
       <c r="R318" t="n">
-        <v>6733190</v>
+        <v>6733246</v>
       </c>
       <c r="S318" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T318" t="inlineStr">
         <is>
@@ -37245,22 +37252,22 @@
       </c>
       <c r="Y318" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
+          <t>2023-08-29</t>
         </is>
       </c>
       <c r="Z318" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA318" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
+          <t>2023-08-29</t>
         </is>
       </c>
       <c r="AB318" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD318" t="b">
@@ -37276,24 +37283,24 @@
       <c r="AT318" t="inlineStr"/>
       <c r="AW318" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX318" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY318" t="inlineStr"/>
       <c r="AZ318" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115535311</t>
+          <t>https://artportalen.se/Sighting/111765246</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="n">
-        <v>121467162</v>
+        <v>115535311</v>
       </c>
       <c r="B319" t="n">
         <v>5179</v>
@@ -37329,17 +37336,17 @@
       <c r="N319" t="inlineStr"/>
       <c r="P319" t="inlineStr">
         <is>
-          <t>Stor Moberg norra, Dlr</t>
+          <t>Leksand, Leksand, Dlr</t>
         </is>
       </c>
       <c r="Q319" t="n">
-        <v>511619</v>
+        <v>511290</v>
       </c>
       <c r="R319" t="n">
-        <v>6733325</v>
+        <v>6733190</v>
       </c>
       <c r="S319" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="T319" t="inlineStr">
         <is>
@@ -37363,12 +37370,22 @@
       </c>
       <c r="Y319" t="inlineStr">
         <is>
-          <t>2024-12-03</t>
+          <t>2024-03-30</t>
+        </is>
+      </c>
+      <c r="Z319" t="inlineStr">
+        <is>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AA319" t="inlineStr">
         <is>
-          <t>2024-12-03</t>
+          <t>2024-03-30</t>
+        </is>
+      </c>
+      <c r="AB319" t="inlineStr">
+        <is>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AD319" t="b">
@@ -37389,19 +37406,19 @@
       </c>
       <c r="AX319" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY319" t="inlineStr"/>
       <c r="AZ319" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121467162</t>
+          <t>https://artportalen.se/Sighting/115535311</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="n">
-        <v>124629152</v>
+        <v>121467162</v>
       </c>
       <c r="B320" t="n">
         <v>5179</v>
@@ -37430,19 +37447,24 @@
         </is>
       </c>
       <c r="I320" t="inlineStr"/>
+      <c r="J320" t="inlineStr"/>
+      <c r="K320" t="inlineStr"/>
+      <c r="L320" t="inlineStr"/>
+      <c r="M320" t="inlineStr"/>
+      <c r="N320" t="inlineStr"/>
       <c r="P320" t="inlineStr">
         <is>
-          <t>Leksand Grim Moberg, Leksand Grim Moberg, Dlr</t>
+          <t>Stor Moberg norra, Dlr</t>
         </is>
       </c>
       <c r="Q320" t="n">
-        <v>511588</v>
+        <v>511619</v>
       </c>
       <c r="R320" t="n">
-        <v>6733314</v>
+        <v>6733325</v>
       </c>
       <c r="S320" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="T320" t="inlineStr">
         <is>
@@ -37466,22 +37488,12 @@
       </c>
       <c r="Y320" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
-        </is>
-      </c>
-      <c r="Z320" t="inlineStr">
-        <is>
-          <t>17:09</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="AA320" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
-        </is>
-      </c>
-      <c r="AB320" t="inlineStr">
-        <is>
-          <t>17:09</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="AD320" t="b">
@@ -37490,30 +37502,31 @@
       <c r="AE320" t="b">
         <v>0</v>
       </c>
+      <c r="AF320" t="inlineStr"/>
       <c r="AG320" t="b">
         <v>0</v>
       </c>
       <c r="AT320" t="inlineStr"/>
       <c r="AW320" t="inlineStr">
         <is>
-          <t>Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX320" t="inlineStr">
         <is>
-          <t>Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY320" t="inlineStr"/>
       <c r="AZ320" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124629152</t>
+          <t>https://artportalen.se/Sighting/121467162</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="n">
-        <v>126411537</v>
+        <v>124629152</v>
       </c>
       <c r="B321" t="n">
         <v>5179</v>
@@ -37542,24 +37555,19 @@
         </is>
       </c>
       <c r="I321" t="inlineStr"/>
-      <c r="J321" t="inlineStr"/>
-      <c r="K321" t="inlineStr"/>
-      <c r="L321" t="inlineStr"/>
-      <c r="M321" t="inlineStr"/>
-      <c r="N321" t="inlineStr"/>
       <c r="P321" t="inlineStr">
         <is>
-          <t>Leksand, Leksand, Dlr</t>
+          <t>Leksand Grim Moberg, Leksand Grim Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q321" t="n">
-        <v>511400</v>
+        <v>511588</v>
       </c>
       <c r="R321" t="n">
-        <v>6733129</v>
+        <v>6733314</v>
       </c>
       <c r="S321" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T321" t="inlineStr">
         <is>
@@ -37583,27 +37591,22 @@
       </c>
       <c r="Y321" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="Z321" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AA321" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="AB321" t="inlineStr">
         <is>
-          <t>14:23</t>
-        </is>
-      </c>
-      <c r="AC321" t="inlineStr">
-        <is>
-          <t>2 döda granar 5 m emellan 6426-6429</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AD321" t="b">
@@ -37612,31 +37615,30 @@
       <c r="AE321" t="b">
         <v>0</v>
       </c>
-      <c r="AF321" t="inlineStr"/>
       <c r="AG321" t="b">
         <v>0</v>
       </c>
       <c r="AT321" t="inlineStr"/>
       <c r="AW321" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Åke Sköld</t>
         </is>
       </c>
       <c r="AX321" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Åke Sköld</t>
         </is>
       </c>
       <c r="AY321" t="inlineStr"/>
       <c r="AZ321" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126411537</t>
+          <t>https://artportalen.se/Sighting/124629152</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="n">
-        <v>126703152</v>
+        <v>126411537</v>
       </c>
       <c r="B322" t="n">
         <v>5179</v>
@@ -37672,14 +37674,14 @@
       <c r="N322" t="inlineStr"/>
       <c r="P322" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Leksand, Leksand, Dlr</t>
         </is>
       </c>
       <c r="Q322" t="n">
-        <v>511586</v>
+        <v>511400</v>
       </c>
       <c r="R322" t="n">
-        <v>6733286</v>
+        <v>6733129</v>
       </c>
       <c r="S322" t="n">
         <v>10</v>
@@ -37711,7 +37713,7 @@
       </c>
       <c r="Z322" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA322" t="inlineStr">
@@ -37721,12 +37723,12 @@
       </c>
       <c r="AB322" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AC322" t="inlineStr">
         <is>
-          <t>6540</t>
+          <t>2 döda granar 5 m emellan 6426-6429</t>
         </is>
       </c>
       <c r="AD322" t="b">
@@ -37753,13 +37755,13 @@
       <c r="AY322" t="inlineStr"/>
       <c r="AZ322" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126703152</t>
+          <t>https://artportalen.se/Sighting/126411537</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="n">
-        <v>127013462</v>
+        <v>126703152</v>
       </c>
       <c r="B323" t="n">
         <v>5179</v>
@@ -37788,16 +37790,21 @@
         </is>
       </c>
       <c r="I323" t="inlineStr"/>
+      <c r="J323" t="inlineStr"/>
+      <c r="K323" t="inlineStr"/>
+      <c r="L323" t="inlineStr"/>
+      <c r="M323" t="inlineStr"/>
+      <c r="N323" t="inlineStr"/>
       <c r="P323" t="inlineStr">
         <is>
-          <t>Stor Moberg norra, Stor Moberg norra, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q323" t="n">
-        <v>511569</v>
+        <v>511586</v>
       </c>
       <c r="R323" t="n">
-        <v>6733489</v>
+        <v>6733286</v>
       </c>
       <c r="S323" t="n">
         <v>10</v>
@@ -37824,27 +37831,27 @@
       </c>
       <c r="Y323" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="Z323" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AA323" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AB323" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AC323" t="inlineStr">
         <is>
-          <t>Flera granar</t>
+          <t>6540</t>
         </is>
       </c>
       <c r="AD323" t="b">
@@ -37853,6 +37860,7 @@
       <c r="AE323" t="b">
         <v>0</v>
       </c>
+      <c r="AF323" t="inlineStr"/>
       <c r="AG323" t="b">
         <v>0</v>
       </c>
@@ -37870,13 +37878,13 @@
       <c r="AY323" t="inlineStr"/>
       <c r="AZ323" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127013462</t>
+          <t>https://artportalen.se/Sighting/126703152</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="n">
-        <v>127031696</v>
+        <v>127013462</v>
       </c>
       <c r="B324" t="n">
         <v>5179</v>
@@ -37905,24 +37913,19 @@
         </is>
       </c>
       <c r="I324" t="inlineStr"/>
-      <c r="J324" t="inlineStr"/>
-      <c r="K324" t="inlineStr"/>
-      <c r="L324" t="inlineStr"/>
-      <c r="M324" t="inlineStr"/>
-      <c r="N324" t="inlineStr"/>
       <c r="P324" t="inlineStr">
         <is>
-          <t>Moberget, Moberget, Dlr</t>
+          <t>Stor Moberg norra, Stor Moberg norra, Dlr</t>
         </is>
       </c>
       <c r="Q324" t="n">
-        <v>511733</v>
+        <v>511569</v>
       </c>
       <c r="R324" t="n">
-        <v>6733336</v>
+        <v>6733489</v>
       </c>
       <c r="S324" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T324" t="inlineStr">
         <is>
@@ -37946,27 +37949,27 @@
       </c>
       <c r="Y324" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="Z324" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="AA324" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="AB324" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="AC324" t="inlineStr">
         <is>
-          <t>Samma låga som doftskinn</t>
+          <t>Flera granar</t>
         </is>
       </c>
       <c r="AD324" t="b">
@@ -37975,31 +37978,30 @@
       <c r="AE324" t="b">
         <v>0</v>
       </c>
-      <c r="AF324" t="inlineStr"/>
       <c r="AG324" t="b">
         <v>0</v>
       </c>
       <c r="AT324" t="inlineStr"/>
       <c r="AW324" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX324" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY324" t="inlineStr"/>
       <c r="AZ324" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127031696</t>
+          <t>https://artportalen.se/Sighting/127013462</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="n">
-        <v>127033428</v>
+        <v>127031696</v>
       </c>
       <c r="B325" t="n">
         <v>5179</v>
@@ -38028,21 +38030,21 @@
         </is>
       </c>
       <c r="I325" t="inlineStr"/>
-      <c r="M325" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+      <c r="J325" t="inlineStr"/>
+      <c r="K325" t="inlineStr"/>
+      <c r="L325" t="inlineStr"/>
+      <c r="M325" t="inlineStr"/>
+      <c r="N325" t="inlineStr"/>
       <c r="P325" t="inlineStr">
         <is>
-          <t>Grim-Moberg, Grim-Moberg, Dlr</t>
+          <t>Moberget, Moberget, Dlr</t>
         </is>
       </c>
       <c r="Q325" t="n">
-        <v>511393</v>
+        <v>511733</v>
       </c>
       <c r="R325" t="n">
-        <v>6733148</v>
+        <v>6733336</v>
       </c>
       <c r="S325" t="n">
         <v>9</v>
@@ -38074,7 +38076,7 @@
       </c>
       <c r="Z325" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA325" t="inlineStr">
@@ -38084,7 +38086,12 @@
       </c>
       <c r="AB325" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AC325" t="inlineStr">
+        <is>
+          <t>Samma låga som doftskinn</t>
         </is>
       </c>
       <c r="AD325" t="b">
@@ -38093,6 +38100,7 @@
       <c r="AE325" t="b">
         <v>0</v>
       </c>
+      <c r="AF325" t="inlineStr"/>
       <c r="AG325" t="b">
         <v>0</v>
       </c>
@@ -38110,13 +38118,13 @@
       <c r="AY325" t="inlineStr"/>
       <c r="AZ325" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127033428</t>
+          <t>https://artportalen.se/Sighting/127031696</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="n">
-        <v>127047707</v>
+        <v>127033428</v>
       </c>
       <c r="B326" t="n">
         <v>5179</v>
@@ -38145,28 +38153,24 @@
         </is>
       </c>
       <c r="I326" t="inlineStr"/>
-      <c r="J326" t="inlineStr"/>
-      <c r="K326" t="inlineStr"/>
-      <c r="L326" t="inlineStr"/>
       <c r="M326" t="inlineStr">
         <is>
           <t>färska gnagspår</t>
         </is>
       </c>
-      <c r="N326" t="inlineStr"/>
       <c r="P326" t="inlineStr">
         <is>
-          <t>Fjällgrycksbo, Dlr</t>
+          <t>Grim-Moberg, Grim-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q326" t="n">
-        <v>511260</v>
+        <v>511393</v>
       </c>
       <c r="R326" t="n">
-        <v>6733233</v>
+        <v>6733148</v>
       </c>
       <c r="S326" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T326" t="inlineStr">
         <is>
@@ -38195,7 +38199,7 @@
       </c>
       <c r="Z326" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AA326" t="inlineStr">
@@ -38205,7 +38209,7 @@
       </c>
       <c r="AB326" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AD326" t="b">
@@ -38214,7 +38218,6 @@
       <c r="AE326" t="b">
         <v>0</v>
       </c>
-      <c r="AF326" t="inlineStr"/>
       <c r="AG326" t="b">
         <v>0</v>
       </c>
@@ -38232,13 +38235,13 @@
       <c r="AY326" t="inlineStr"/>
       <c r="AZ326" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127047707</t>
+          <t>https://artportalen.se/Sighting/127033428</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="n">
-        <v>127047841</v>
+        <v>127047707</v>
       </c>
       <c r="B327" t="n">
         <v>5179</v>
@@ -38272,7 +38275,7 @@
       <c r="L327" t="inlineStr"/>
       <c r="M327" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N327" t="inlineStr"/>
@@ -38282,10 +38285,10 @@
         </is>
       </c>
       <c r="Q327" t="n">
-        <v>511199</v>
+        <v>511260</v>
       </c>
       <c r="R327" t="n">
-        <v>6733259</v>
+        <v>6733233</v>
       </c>
       <c r="S327" t="n">
         <v>10</v>
@@ -38317,7 +38320,7 @@
       </c>
       <c r="Z327" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AA327" t="inlineStr">
@@ -38327,7 +38330,7 @@
       </c>
       <c r="AB327" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AD327" t="b">
@@ -38354,13 +38357,13 @@
       <c r="AY327" t="inlineStr"/>
       <c r="AZ327" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127047841</t>
+          <t>https://artportalen.se/Sighting/127047707</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="n">
-        <v>127048044</v>
+        <v>127047841</v>
       </c>
       <c r="B328" t="n">
         <v>5179</v>
@@ -38394,7 +38397,7 @@
       <c r="L328" t="inlineStr"/>
       <c r="M328" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N328" t="inlineStr"/>
@@ -38404,10 +38407,10 @@
         </is>
       </c>
       <c r="Q328" t="n">
-        <v>511187</v>
+        <v>511199</v>
       </c>
       <c r="R328" t="n">
-        <v>6733200</v>
+        <v>6733259</v>
       </c>
       <c r="S328" t="n">
         <v>10</v>
@@ -38439,7 +38442,7 @@
       </c>
       <c r="Z328" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA328" t="inlineStr">
@@ -38449,7 +38452,7 @@
       </c>
       <c r="AB328" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD328" t="b">
@@ -38476,13 +38479,13 @@
       <c r="AY328" t="inlineStr"/>
       <c r="AZ328" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127048044</t>
+          <t>https://artportalen.se/Sighting/127047841</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="n">
-        <v>127048201</v>
+        <v>127048044</v>
       </c>
       <c r="B329" t="n">
         <v>5179</v>
@@ -38522,14 +38525,14 @@
       <c r="N329" t="inlineStr"/>
       <c r="P329" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Fjällgrycksbo, Dlr</t>
         </is>
       </c>
       <c r="Q329" t="n">
-        <v>511253</v>
+        <v>511187</v>
       </c>
       <c r="R329" t="n">
-        <v>6733209</v>
+        <v>6733200</v>
       </c>
       <c r="S329" t="n">
         <v>10</v>
@@ -38561,7 +38564,7 @@
       </c>
       <c r="Z329" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA329" t="inlineStr">
@@ -38571,7 +38574,7 @@
       </c>
       <c r="AB329" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AD329" t="b">
@@ -38598,13 +38601,13 @@
       <c r="AY329" t="inlineStr"/>
       <c r="AZ329" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127048201</t>
+          <t>https://artportalen.se/Sighting/127048044</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="n">
-        <v>127085455</v>
+        <v>127048201</v>
       </c>
       <c r="B330" t="n">
         <v>5179</v>
@@ -38633,21 +38636,25 @@
         </is>
       </c>
       <c r="I330" t="inlineStr"/>
+      <c r="J330" t="inlineStr"/>
+      <c r="K330" t="inlineStr"/>
+      <c r="L330" t="inlineStr"/>
       <c r="M330" t="inlineStr">
         <is>
           <t>färska gnagspår</t>
         </is>
       </c>
+      <c r="N330" t="inlineStr"/>
       <c r="P330" t="inlineStr">
         <is>
-          <t>Stor-Moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q330" t="n">
-        <v>511741</v>
+        <v>511253</v>
       </c>
       <c r="R330" t="n">
-        <v>6733263</v>
+        <v>6733209</v>
       </c>
       <c r="S330" t="n">
         <v>10</v>
@@ -38674,12 +38681,22 @@
       </c>
       <c r="Y330" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="Z330" t="inlineStr">
+        <is>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA330" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AB330" t="inlineStr">
+        <is>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD330" t="b">
@@ -38688,30 +38705,31 @@
       <c r="AE330" t="b">
         <v>0</v>
       </c>
+      <c r="AF330" t="inlineStr"/>
       <c r="AG330" t="b">
         <v>0</v>
       </c>
       <c r="AT330" t="inlineStr"/>
       <c r="AW330" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX330" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY330" t="inlineStr"/>
       <c r="AZ330" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127085455</t>
+          <t>https://artportalen.se/Sighting/127048201</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="n">
-        <v>127154592</v>
+        <v>127085455</v>
       </c>
       <c r="B331" t="n">
         <v>5179</v>
@@ -38742,22 +38760,22 @@
       <c r="I331" t="inlineStr"/>
       <c r="M331" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P331" t="inlineStr">
         <is>
-          <t>Moberget, Moberget, Dlr</t>
+          <t>Stor-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q331" t="n">
-        <v>511702</v>
+        <v>511741</v>
       </c>
       <c r="R331" t="n">
-        <v>6733305</v>
+        <v>6733263</v>
       </c>
       <c r="S331" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T331" t="inlineStr">
         <is>
@@ -38781,22 +38799,12 @@
       </c>
       <c r="Y331" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
-        </is>
-      </c>
-      <c r="Z331" t="inlineStr">
-        <is>
-          <t>15:26</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="AA331" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
-        </is>
-      </c>
-      <c r="AB331" t="inlineStr">
-        <is>
-          <t>15:26</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="AD331" t="b">
@@ -38811,24 +38819,24 @@
       <c r="AT331" t="inlineStr"/>
       <c r="AW331" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX331" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY331" t="inlineStr"/>
       <c r="AZ331" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127154592</t>
+          <t>https://artportalen.se/Sighting/127085455</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="n">
-        <v>129170584</v>
+        <v>127154592</v>
       </c>
       <c r="B332" t="n">
         <v>5179</v>
@@ -38857,19 +38865,24 @@
         </is>
       </c>
       <c r="I332" t="inlineStr"/>
+      <c r="M332" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P332" t="inlineStr">
         <is>
-          <t>Leksand, Leksand, Dlr</t>
+          <t>Moberget, Moberget, Dlr</t>
         </is>
       </c>
       <c r="Q332" t="n">
-        <v>511274</v>
+        <v>511702</v>
       </c>
       <c r="R332" t="n">
-        <v>6733128</v>
+        <v>6733305</v>
       </c>
       <c r="S332" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T332" t="inlineStr">
         <is>
@@ -38893,22 +38906,22 @@
       </c>
       <c r="Y332" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="Z332" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA332" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="AB332" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD332" t="b">
@@ -38923,27 +38936,27 @@
       <c r="AT332" t="inlineStr"/>
       <c r="AW332" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX332" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY332" t="inlineStr"/>
       <c r="AZ332" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129170584</t>
+          <t>https://artportalen.se/Sighting/127154592</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="n">
-        <v>133343553</v>
+        <v>129170584</v>
       </c>
       <c r="B333" t="n">
-        <v>5181</v>
+        <v>5179</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -38969,24 +38982,19 @@
         </is>
       </c>
       <c r="I333" t="inlineStr"/>
-      <c r="J333" t="inlineStr"/>
-      <c r="K333" t="inlineStr"/>
-      <c r="L333" t="inlineStr"/>
-      <c r="M333" t="inlineStr"/>
-      <c r="N333" t="inlineStr"/>
       <c r="P333" t="inlineStr">
         <is>
-          <t>Grim Moberg , Dlr</t>
+          <t>Leksand, Leksand, Dlr</t>
         </is>
       </c>
       <c r="Q333" t="n">
-        <v>511591</v>
+        <v>511274</v>
       </c>
       <c r="R333" t="n">
-        <v>6733260</v>
+        <v>6733128</v>
       </c>
       <c r="S333" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T333" t="inlineStr">
         <is>
@@ -39010,22 +39018,22 @@
       </c>
       <c r="Y333" t="inlineStr">
         <is>
-          <t>2024-04-13</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="Z333" t="inlineStr">
         <is>
-          <t>17:34</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA333" t="inlineStr">
         <is>
-          <t>2024-04-13</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AB333" t="inlineStr">
         <is>
-          <t>17:34</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD333" t="b">
@@ -39034,7 +39042,6 @@
       <c r="AE333" t="b">
         <v>0</v>
       </c>
-      <c r="AF333" t="inlineStr"/>
       <c r="AG333" t="b">
         <v>0</v>
       </c>
@@ -39052,13 +39059,13 @@
       <c r="AY333" t="inlineStr"/>
       <c r="AZ333" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133343553</t>
+          <t>https://artportalen.se/Sighting/129170584</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="n">
-        <v>134624221</v>
+        <v>133343553</v>
       </c>
       <c r="B334" t="n">
         <v>5181</v>
@@ -39090,25 +39097,21 @@
       <c r="J334" t="inlineStr"/>
       <c r="K334" t="inlineStr"/>
       <c r="L334" t="inlineStr"/>
-      <c r="M334" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M334" t="inlineStr"/>
       <c r="N334" t="inlineStr"/>
       <c r="P334" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Grim Moberg , Dlr</t>
         </is>
       </c>
       <c r="Q334" t="n">
-        <v>511576</v>
+        <v>511591</v>
       </c>
       <c r="R334" t="n">
-        <v>6733279</v>
+        <v>6733260</v>
       </c>
       <c r="S334" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T334" t="inlineStr">
         <is>
@@ -39132,27 +39135,22 @@
       </c>
       <c r="Y334" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2024-04-13</t>
         </is>
       </c>
       <c r="Z334" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>17:34</t>
         </is>
       </c>
       <c r="AA334" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2024-04-13</t>
         </is>
       </c>
       <c r="AB334" t="inlineStr">
         <is>
-          <t>16:25</t>
-        </is>
-      </c>
-      <c r="AC334" t="inlineStr">
-        <is>
-          <t>På låga med med doftskinn.</t>
+          <t>17:34</t>
         </is>
       </c>
       <c r="AD334" t="b">
@@ -39179,59 +39177,63 @@
       <c r="AY334" t="inlineStr"/>
       <c r="AZ334" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134624221</t>
+          <t>https://artportalen.se/Sighting/133343553</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="n">
-        <v>127152893</v>
+        <v>134624221</v>
       </c>
       <c r="B335" t="n">
-        <v>5178</v>
+        <v>5181</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E335" t="n">
-        <v>102204</v>
+        <v>100526</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>Grönhjon</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H335" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I335" t="inlineStr"/>
+      <c r="J335" t="inlineStr"/>
+      <c r="K335" t="inlineStr"/>
+      <c r="L335" t="inlineStr"/>
       <c r="M335" t="inlineStr">
         <is>
           <t>äldre gnagspår</t>
         </is>
       </c>
+      <c r="N335" t="inlineStr"/>
       <c r="P335" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q335" t="n">
-        <v>511720</v>
+        <v>511576</v>
       </c>
       <c r="R335" t="n">
-        <v>6733228</v>
+        <v>6733279</v>
       </c>
       <c r="S335" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T335" t="inlineStr">
         <is>
@@ -39255,22 +39257,27 @@
       </c>
       <c r="Y335" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="Z335" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA335" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="AB335" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="AC335" t="inlineStr">
+        <is>
+          <t>På låga med med doftskinn.</t>
         </is>
       </c>
       <c r="AD335" t="b">
@@ -39279,79 +39286,77 @@
       <c r="AE335" t="b">
         <v>0</v>
       </c>
+      <c r="AF335" t="inlineStr"/>
       <c r="AG335" t="b">
         <v>0</v>
       </c>
       <c r="AT335" t="inlineStr"/>
       <c r="AW335" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX335" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY335" t="inlineStr"/>
       <c r="AZ335" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127152893</t>
+          <t>https://artportalen.se/Sighting/134624221</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="n">
-        <v>123767919</v>
+        <v>127152893</v>
       </c>
       <c r="B336" t="n">
-        <v>57132</v>
+        <v>5178</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E336" t="n">
-        <v>102612</v>
+        <v>102204</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Grönhjon</t>
         </is>
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H336" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(De Geer, 1775)</t>
         </is>
       </c>
       <c r="I336" t="inlineStr"/>
-      <c r="K336" t="inlineStr"/>
-      <c r="L336" t="inlineStr"/>
       <c r="M336" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N336" t="inlineStr"/>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P336" t="inlineStr">
         <is>
           <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q336" t="n">
-        <v>511689</v>
+        <v>511720</v>
       </c>
       <c r="R336" t="n">
-        <v>6733227</v>
+        <v>6733228</v>
       </c>
       <c r="S336" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T336" t="inlineStr">
         <is>
@@ -39375,27 +39380,22 @@
       </c>
       <c r="Y336" t="inlineStr">
         <is>
-          <t>2025-03-21</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="Z336" t="inlineStr">
         <is>
-          <t>08:47</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA336" t="inlineStr">
         <is>
-          <t>2025-03-21</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="AB336" t="inlineStr">
         <is>
-          <t>08:47</t>
-        </is>
-      </c>
-      <c r="AC336" t="inlineStr">
-        <is>
-          <t>Eftersom Sjös Moberg nu saknar skydd mot avverkning släpper jag de ca 100 dolda fynden som bara SKS har kunnat se. När den gamla fäbodskogen avverkas ska alla kunna se vilka naturvärden den innehöll när den avverkades. Tjädermöten och spelplatser frånräknade.</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD336" t="b">
@@ -39410,24 +39410,24 @@
       <c r="AT336" t="inlineStr"/>
       <c r="AW336" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX336" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY336" t="inlineStr"/>
       <c r="AZ336" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123767919</t>
+          <t>https://artportalen.se/Sighting/127152893</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="n">
-        <v>126688753</v>
+        <v>123767919</v>
       </c>
       <c r="B337" t="n">
         <v>57132</v>
@@ -39458,21 +39458,25 @@
       <c r="I337" t="inlineStr"/>
       <c r="K337" t="inlineStr"/>
       <c r="L337" t="inlineStr"/>
-      <c r="M337" t="inlineStr"/>
+      <c r="M337" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N337" t="inlineStr"/>
       <c r="P337" t="inlineStr">
         <is>
-          <t>Grim Moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q337" t="n">
-        <v>511597</v>
+        <v>511689</v>
       </c>
       <c r="R337" t="n">
-        <v>6733262</v>
+        <v>6733227</v>
       </c>
       <c r="S337" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T337" t="inlineStr">
         <is>
@@ -39496,27 +39500,27 @@
       </c>
       <c r="Y337" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="Z337" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="AA337" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="AB337" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="AC337" t="inlineStr">
         <is>
-          <t>spillning på en upphöjd häll med renlav och mossa i blåbärsskog, mindre än tjäder, gamla tallar och granar,</t>
+          <t>Eftersom Sjös Moberg nu saknar skydd mot avverkning släpper jag de ca 100 dolda fynden som bara SKS har kunnat se. När den gamla fäbodskogen avverkas ska alla kunna se vilka naturvärden den innehöll när den avverkades. Tjädermöten och spelplatser frånräknade.</t>
         </is>
       </c>
       <c r="AD337" t="b">
@@ -39536,19 +39540,19 @@
       </c>
       <c r="AX337" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY337" t="inlineStr"/>
       <c r="AZ337" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126688753</t>
+          <t>https://artportalen.se/Sighting/123767919</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="n">
-        <v>126688754</v>
+        <v>126688753</v>
       </c>
       <c r="B338" t="n">
         <v>57132</v>
@@ -39579,11 +39583,7 @@
       <c r="I338" t="inlineStr"/>
       <c r="K338" t="inlineStr"/>
       <c r="L338" t="inlineStr"/>
-      <c r="M338" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
+      <c r="M338" t="inlineStr"/>
       <c r="N338" t="inlineStr"/>
       <c r="P338" t="inlineStr">
         <is>
@@ -39591,10 +39591,10 @@
         </is>
       </c>
       <c r="Q338" t="n">
-        <v>511499</v>
+        <v>511597</v>
       </c>
       <c r="R338" t="n">
-        <v>6733244</v>
+        <v>6733262</v>
       </c>
       <c r="S338" t="n">
         <v>10</v>
@@ -39626,7 +39626,7 @@
       </c>
       <c r="Z338" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AA338" t="inlineStr">
@@ -39636,12 +39636,12 @@
       </c>
       <c r="AB338" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AC338" t="inlineStr">
         <is>
-          <t>Betydligt mindre än tjäder, men på en liten höjd hällmark och lite uppriven renlav låg spillning, jag har kollekt</t>
+          <t>spillning på en upphöjd häll med renlav och mossa i blåbärsskog, mindre än tjäder, gamla tallar och granar,</t>
         </is>
       </c>
       <c r="AD338" t="b">
@@ -39667,33 +39667,33 @@
       <c r="AY338" t="inlineStr"/>
       <c r="AZ338" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126688754</t>
+          <t>https://artportalen.se/Sighting/126688753</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="n">
-        <v>127014946</v>
+        <v>126688754</v>
       </c>
       <c r="B339" t="n">
-        <v>57774</v>
+        <v>57132</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E339" t="n">
-        <v>102976</v>
+        <v>102612</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H339" t="inlineStr">
@@ -39702,16 +39702,24 @@
         </is>
       </c>
       <c r="I339" t="inlineStr"/>
+      <c r="K339" t="inlineStr"/>
+      <c r="L339" t="inlineStr"/>
+      <c r="M339" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N339" t="inlineStr"/>
       <c r="P339" t="inlineStr">
         <is>
-          <t>Stor Moberg norra, Stor Moberg norra, Dlr</t>
+          <t>Grim Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q339" t="n">
-        <v>511699</v>
+        <v>511499</v>
       </c>
       <c r="R339" t="n">
-        <v>6733622</v>
+        <v>6733244</v>
       </c>
       <c r="S339" t="n">
         <v>10</v>
@@ -39738,22 +39746,27 @@
       </c>
       <c r="Y339" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="Z339" t="inlineStr">
         <is>
-          <t>20:33</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA339" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AB339" t="inlineStr">
         <is>
-          <t>20:33</t>
+          <t>17:06</t>
+        </is>
+      </c>
+      <c r="AC339" t="inlineStr">
+        <is>
+          <t>Betydligt mindre än tjäder, men på en liten höjd hällmark och lite uppriven renlav låg spillning, jag har kollekt</t>
         </is>
       </c>
       <c r="AD339" t="b">
@@ -39779,59 +39792,51 @@
       <c r="AY339" t="inlineStr"/>
       <c r="AZ339" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127014946</t>
+          <t>https://artportalen.se/Sighting/126688754</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="n">
-        <v>124633056</v>
+        <v>127014946</v>
       </c>
       <c r="B340" t="n">
-        <v>58388</v>
+        <v>57774</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E340" t="n">
-        <v>103001</v>
+        <v>102976</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I340" t="inlineStr"/>
-      <c r="K340" t="inlineStr"/>
-      <c r="L340" t="inlineStr"/>
-      <c r="M340" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N340" t="inlineStr"/>
       <c r="P340" t="inlineStr">
         <is>
-          <t>Moberg, Moberg, Dlr</t>
+          <t>Stor Moberg norra, Stor Moberg norra, Dlr</t>
         </is>
       </c>
       <c r="Q340" t="n">
-        <v>511691</v>
+        <v>511699</v>
       </c>
       <c r="R340" t="n">
-        <v>6733344</v>
+        <v>6733622</v>
       </c>
       <c r="S340" t="n">
         <v>10</v>
@@ -39858,22 +39863,22 @@
       </c>
       <c r="Y340" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="Z340" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>20:33</t>
         </is>
       </c>
       <c r="AA340" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="AB340" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>20:33</t>
         </is>
       </c>
       <c r="AD340" t="b">
@@ -39893,57 +39898,65 @@
       </c>
       <c r="AX340" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY340" t="inlineStr"/>
       <c r="AZ340" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124633056</t>
+          <t>https://artportalen.se/Sighting/127014946</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="n">
-        <v>126413105</v>
+        <v>124633056</v>
       </c>
       <c r="B341" t="n">
-        <v>58327</v>
+        <v>58388</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E341" t="n">
-        <v>103015</v>
+        <v>103001</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H341" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I341" t="inlineStr"/>
+      <c r="K341" t="inlineStr"/>
+      <c r="L341" t="inlineStr"/>
+      <c r="M341" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N341" t="inlineStr"/>
       <c r="P341" t="inlineStr">
         <is>
-          <t>Leksand, Leksand, Dlr</t>
+          <t>Moberg, Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q341" t="n">
-        <v>511404</v>
+        <v>511691</v>
       </c>
       <c r="R341" t="n">
-        <v>6733198</v>
+        <v>6733344</v>
       </c>
       <c r="S341" t="n">
         <v>10</v>
@@ -39970,22 +39983,22 @@
       </c>
       <c r="Y341" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="Z341" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AA341" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="AB341" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AD341" t="b">
@@ -40005,19 +40018,19 @@
       </c>
       <c r="AX341" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY341" t="inlineStr"/>
       <c r="AZ341" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126413105</t>
+          <t>https://artportalen.se/Sighting/124633056</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="n">
-        <v>127014469</v>
+        <v>126413105</v>
       </c>
       <c r="B342" t="n">
         <v>58327</v>
@@ -40048,14 +40061,14 @@
       <c r="I342" t="inlineStr"/>
       <c r="P342" t="inlineStr">
         <is>
-          <t>Stor Moberg norra, Stor Moberg norra, Dlr</t>
+          <t>Leksand, Leksand, Dlr</t>
         </is>
       </c>
       <c r="Q342" t="n">
-        <v>511665</v>
+        <v>511404</v>
       </c>
       <c r="R342" t="n">
-        <v>6733624</v>
+        <v>6733198</v>
       </c>
       <c r="S342" t="n">
         <v>10</v>
@@ -40082,22 +40095,22 @@
       </c>
       <c r="Y342" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="Z342" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA342" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AB342" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD342" t="b">
@@ -40123,13 +40136,13 @@
       <c r="AY342" t="inlineStr"/>
       <c r="AZ342" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127014469</t>
+          <t>https://artportalen.se/Sighting/126413105</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="n">
-        <v>127014933</v>
+        <v>127014469</v>
       </c>
       <c r="B343" t="n">
         <v>58327</v>
@@ -40164,10 +40177,10 @@
         </is>
       </c>
       <c r="Q343" t="n">
-        <v>511699</v>
+        <v>511665</v>
       </c>
       <c r="R343" t="n">
-        <v>6733622</v>
+        <v>6733624</v>
       </c>
       <c r="S343" t="n">
         <v>10</v>
@@ -40199,7 +40212,7 @@
       </c>
       <c r="Z343" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="AA343" t="inlineStr">
@@ -40209,7 +40222,7 @@
       </c>
       <c r="AB343" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="AD343" t="b">
@@ -40235,68 +40248,54 @@
       <c r="AY343" t="inlineStr"/>
       <c r="AZ343" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127014933</t>
+          <t>https://artportalen.se/Sighting/127014469</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="n">
-        <v>104872335</v>
+        <v>127014933</v>
       </c>
       <c r="B344" t="n">
-        <v>58114</v>
+        <v>58327</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E344" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H344" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I344" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K344" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M344" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I344" t="inlineStr"/>
       <c r="P344" t="inlineStr">
         <is>
-          <t>Leksand Moberg, Dlr</t>
+          <t>Stor Moberg norra, Stor Moberg norra, Dlr</t>
         </is>
       </c>
       <c r="Q344" t="n">
-        <v>511294</v>
+        <v>511699</v>
       </c>
       <c r="R344" t="n">
-        <v>6733102</v>
+        <v>6733622</v>
       </c>
       <c r="S344" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T344" t="inlineStr">
         <is>
@@ -40320,22 +40319,22 @@
       </c>
       <c r="Y344" t="inlineStr">
         <is>
-          <t>2022-12-01</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="Z344" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="AA344" t="inlineStr">
         <is>
-          <t>2022-12-01</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="AB344" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="AD344" t="b">
@@ -40350,24 +40349,24 @@
       <c r="AT344" t="inlineStr"/>
       <c r="AW344" t="inlineStr">
         <is>
-          <t>Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX344" t="inlineStr">
         <is>
-          <t>Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY344" t="inlineStr"/>
       <c r="AZ344" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104872335</t>
+          <t>https://artportalen.se/Sighting/127014933</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="n">
-        <v>105090857</v>
+        <v>104872335</v>
       </c>
       <c r="B345" t="n">
         <v>58114</v>
@@ -40397,23 +40396,29 @@
       </c>
       <c r="I345" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K345" t="inlineStr"/>
-      <c r="L345" t="inlineStr"/>
-      <c r="M345" t="inlineStr"/>
-      <c r="N345" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K345" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M345" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P345" t="inlineStr">
         <is>
-          <t>Moberget, Dlr</t>
+          <t>Leksand Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q345" t="n">
-        <v>511291</v>
+        <v>511294</v>
       </c>
       <c r="R345" t="n">
-        <v>6733112</v>
+        <v>6733102</v>
       </c>
       <c r="S345" t="n">
         <v>25</v>
@@ -40440,17 +40445,22 @@
       </c>
       <c r="Y345" t="inlineStr">
         <is>
-          <t>2022-12-04</t>
+          <t>2022-12-01</t>
+        </is>
+      </c>
+      <c r="Z345" t="inlineStr">
+        <is>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA345" t="inlineStr">
         <is>
-          <t>2022-12-04</t>
-        </is>
-      </c>
-      <c r="AC345" t="inlineStr">
-        <is>
-          <t>Minst två ex</t>
+          <t>2022-12-01</t>
+        </is>
+      </c>
+      <c r="AB345" t="inlineStr">
+        <is>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD345" t="b">
@@ -40465,24 +40475,24 @@
       <c r="AT345" t="inlineStr"/>
       <c r="AW345" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Åke Sköld</t>
         </is>
       </c>
       <c r="AX345" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Åke Sköld</t>
         </is>
       </c>
       <c r="AY345" t="inlineStr"/>
       <c r="AZ345" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/105090857</t>
+          <t>https://artportalen.se/Sighting/104872335</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="n">
-        <v>106954216</v>
+        <v>105090857</v>
       </c>
       <c r="B346" t="n">
         <v>58114</v>
@@ -40512,31 +40522,23 @@
       </c>
       <c r="I346" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K346" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K346" t="inlineStr"/>
       <c r="L346" t="inlineStr"/>
-      <c r="M346" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="M346" t="inlineStr"/>
       <c r="N346" t="inlineStr"/>
       <c r="P346" t="inlineStr">
         <is>
-          <t>Moberg, Kilen-Stor, Moberg, Leksand, Dlr</t>
+          <t>Moberget, Dlr</t>
         </is>
       </c>
       <c r="Q346" t="n">
-        <v>511354</v>
+        <v>511291</v>
       </c>
       <c r="R346" t="n">
-        <v>6733276</v>
+        <v>6733112</v>
       </c>
       <c r="S346" t="n">
         <v>25</v>
@@ -40563,22 +40565,17 @@
       </c>
       <c r="Y346" t="inlineStr">
         <is>
-          <t>2023-02-21</t>
-        </is>
-      </c>
-      <c r="Z346" t="inlineStr">
-        <is>
-          <t>14:30</t>
+          <t>2022-12-04</t>
         </is>
       </c>
       <c r="AA346" t="inlineStr">
         <is>
-          <t>2023-02-21</t>
-        </is>
-      </c>
-      <c r="AB346" t="inlineStr">
-        <is>
-          <t>14:30</t>
+          <t>2022-12-04</t>
+        </is>
+      </c>
+      <c r="AC346" t="inlineStr">
+        <is>
+          <t>Minst två ex</t>
         </is>
       </c>
       <c r="AD346" t="b">
@@ -40593,24 +40590,24 @@
       <c r="AT346" t="inlineStr"/>
       <c r="AW346" t="inlineStr">
         <is>
-          <t>Lars Johan Klockars</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX346" t="inlineStr">
         <is>
-          <t>Lars Johan Klockars</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY346" t="inlineStr"/>
       <c r="AZ346" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/106954216</t>
+          <t>https://artportalen.se/Sighting/105090857</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="n">
-        <v>109602181</v>
+        <v>106954216</v>
       </c>
       <c r="B347" t="n">
         <v>58114</v>
@@ -40643,12 +40640,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K347" t="inlineStr"/>
-      <c r="L347" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="K347" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L347" t="inlineStr"/>
       <c r="M347" t="inlineStr">
         <is>
           <t>spel/sång</t>
@@ -40657,17 +40654,17 @@
       <c r="N347" t="inlineStr"/>
       <c r="P347" t="inlineStr">
         <is>
-          <t>Moberget, Dlr</t>
+          <t>Moberg, Kilen-Stor, Moberg, Leksand, Dlr</t>
         </is>
       </c>
       <c r="Q347" t="n">
-        <v>511120</v>
+        <v>511354</v>
       </c>
       <c r="R347" t="n">
-        <v>6733224</v>
+        <v>6733276</v>
       </c>
       <c r="S347" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T347" t="inlineStr">
         <is>
@@ -40691,12 +40688,22 @@
       </c>
       <c r="Y347" t="inlineStr">
         <is>
-          <t>2023-03-30</t>
+          <t>2023-02-21</t>
+        </is>
+      </c>
+      <c r="Z347" t="inlineStr">
+        <is>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA347" t="inlineStr">
         <is>
-          <t>2023-03-30</t>
+          <t>2023-02-21</t>
+        </is>
+      </c>
+      <c r="AB347" t="inlineStr">
+        <is>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD347" t="b">
@@ -40711,24 +40718,24 @@
       <c r="AT347" t="inlineStr"/>
       <c r="AW347" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lars Johan Klockars</t>
         </is>
       </c>
       <c r="AX347" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lars Johan Klockars</t>
         </is>
       </c>
       <c r="AY347" t="inlineStr"/>
       <c r="AZ347" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/109602181</t>
+          <t>https://artportalen.se/Sighting/106954216</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="n">
-        <v>120515014</v>
+        <v>109602181</v>
       </c>
       <c r="B348" t="n">
         <v>58114</v>
@@ -40756,28 +40763,36 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I348" t="inlineStr"/>
+      <c r="I348" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K348" t="inlineStr"/>
-      <c r="L348" t="inlineStr"/>
+      <c r="L348" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M348" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N348" t="inlineStr"/>
       <c r="P348" t="inlineStr">
         <is>
-          <t>Leksand, Dlr</t>
+          <t>Moberget, Dlr</t>
         </is>
       </c>
       <c r="Q348" t="n">
-        <v>511388</v>
+        <v>511120</v>
       </c>
       <c r="R348" t="n">
-        <v>6733145</v>
+        <v>6733224</v>
       </c>
       <c r="S348" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T348" t="inlineStr">
         <is>
@@ -40801,27 +40816,12 @@
       </c>
       <c r="Y348" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
-        </is>
-      </c>
-      <c r="Z348" t="inlineStr">
-        <is>
-          <t>13:01</t>
+          <t>2023-03-30</t>
         </is>
       </c>
       <c r="AA348" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
-        </is>
-      </c>
-      <c r="AB348" t="inlineStr">
-        <is>
-          <t>13:01</t>
-        </is>
-      </c>
-      <c r="AC348" t="inlineStr">
-        <is>
-          <t>Den gav sig till känna. Den lät som talltitor låter en höstdag i skogen.</t>
+          <t>2023-03-30</t>
         </is>
       </c>
       <c r="AD348" t="b">
@@ -40836,24 +40836,24 @@
       <c r="AT348" t="inlineStr"/>
       <c r="AW348" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX348" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY348" t="inlineStr"/>
       <c r="AZ348" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120515014</t>
+          <t>https://artportalen.se/Sighting/109602181</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="n">
-        <v>121401512</v>
+        <v>120515014</v>
       </c>
       <c r="B349" t="n">
         <v>58114</v>
@@ -40884,18 +40884,22 @@
       <c r="I349" t="inlineStr"/>
       <c r="K349" t="inlineStr"/>
       <c r="L349" t="inlineStr"/>
-      <c r="M349" t="inlineStr"/>
+      <c r="M349" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N349" t="inlineStr"/>
       <c r="P349" t="inlineStr">
         <is>
-          <t>Hackmora, Dlr</t>
+          <t>Leksand, Dlr</t>
         </is>
       </c>
       <c r="Q349" t="n">
-        <v>511967</v>
+        <v>511388</v>
       </c>
       <c r="R349" t="n">
-        <v>6733388</v>
+        <v>6733145</v>
       </c>
       <c r="S349" t="n">
         <v>25</v>
@@ -40922,27 +40926,27 @@
       </c>
       <c r="Y349" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-10-20</t>
         </is>
       </c>
       <c r="Z349" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA349" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-10-20</t>
         </is>
       </c>
       <c r="AB349" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AC349" t="inlineStr">
         <is>
-          <t>Miljöbilder,</t>
+          <t>Den gav sig till känna. Den lät som talltitor låter en höstdag i skogen.</t>
         </is>
       </c>
       <c r="AD349" t="b">
@@ -40962,19 +40966,19 @@
       </c>
       <c r="AX349" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY349" t="inlineStr"/>
       <c r="AZ349" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121401512</t>
+          <t>https://artportalen.se/Sighting/120515014</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="n">
-        <v>127014013</v>
+        <v>121401512</v>
       </c>
       <c r="B350" t="n">
         <v>58114</v>
@@ -41003,19 +41007,23 @@
         </is>
       </c>
       <c r="I350" t="inlineStr"/>
+      <c r="K350" t="inlineStr"/>
+      <c r="L350" t="inlineStr"/>
+      <c r="M350" t="inlineStr"/>
+      <c r="N350" t="inlineStr"/>
       <c r="P350" t="inlineStr">
         <is>
-          <t>Stor Moberg norra, Stor Moberg norra, Dlr</t>
+          <t>Hackmora, Dlr</t>
         </is>
       </c>
       <c r="Q350" t="n">
-        <v>511594</v>
+        <v>511967</v>
       </c>
       <c r="R350" t="n">
-        <v>6733536</v>
+        <v>6733388</v>
       </c>
       <c r="S350" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T350" t="inlineStr">
         <is>
@@ -41039,22 +41047,27 @@
       </c>
       <c r="Y350" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="Z350" t="inlineStr">
         <is>
-          <t>19:51</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA350" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AB350" t="inlineStr">
         <is>
-          <t>19:51</t>
+          <t>10:33</t>
+        </is>
+      </c>
+      <c r="AC350" t="inlineStr">
+        <is>
+          <t>Miljöbilder,</t>
         </is>
       </c>
       <c r="AD350" t="b">
@@ -41080,13 +41093,13 @@
       <c r="AY350" t="inlineStr"/>
       <c r="AZ350" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127014013</t>
+          <t>https://artportalen.se/Sighting/121401512</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="n">
-        <v>127784860</v>
+        <v>127014013</v>
       </c>
       <c r="B351" t="n">
         <v>58114</v>
@@ -41117,14 +41130,14 @@
       <c r="I351" t="inlineStr"/>
       <c r="P351" t="inlineStr">
         <is>
-          <t>Sjös Moberg, Dlr</t>
+          <t>Stor Moberg norra, Stor Moberg norra, Dlr</t>
         </is>
       </c>
       <c r="Q351" t="n">
-        <v>511669</v>
+        <v>511594</v>
       </c>
       <c r="R351" t="n">
-        <v>6733230</v>
+        <v>6733536</v>
       </c>
       <c r="S351" t="n">
         <v>10</v>
@@ -41151,12 +41164,22 @@
       </c>
       <c r="Y351" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="Z351" t="inlineStr">
+        <is>
+          <t>19:51</t>
         </is>
       </c>
       <c r="AA351" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AB351" t="inlineStr">
+        <is>
+          <t>19:51</t>
         </is>
       </c>
       <c r="AD351" t="b">
@@ -41171,70 +41194,62 @@
       <c r="AT351" t="inlineStr"/>
       <c r="AW351" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX351" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY351" t="inlineStr"/>
       <c r="AZ351" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127784860</t>
+          <t>https://artportalen.se/Sighting/127014013</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="n">
-        <v>124629179</v>
+        <v>127784860</v>
       </c>
       <c r="B352" t="n">
-        <v>58636</v>
+        <v>58114</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E352" t="n">
-        <v>103044</v>
+        <v>103021</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G352" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H352" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I352" t="inlineStr"/>
-      <c r="K352" t="inlineStr"/>
-      <c r="L352" t="inlineStr"/>
-      <c r="M352" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N352" t="inlineStr"/>
       <c r="P352" t="inlineStr">
         <is>
-          <t>Moberg, Moberg, Dlr</t>
+          <t>Sjös Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q352" t="n">
-        <v>511558</v>
+        <v>511669</v>
       </c>
       <c r="R352" t="n">
-        <v>6733323</v>
+        <v>6733230</v>
       </c>
       <c r="S352" t="n">
         <v>10</v>
@@ -41261,27 +41276,12 @@
       </c>
       <c r="Y352" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
-        </is>
-      </c>
-      <c r="Z352" t="inlineStr">
-        <is>
-          <t>17:02</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="AA352" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
-        </is>
-      </c>
-      <c r="AB352" t="inlineStr">
-        <is>
-          <t>17:02</t>
-        </is>
-      </c>
-      <c r="AC352" t="inlineStr">
-        <is>
-          <t>Bofink Koltrast</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="AD352" t="b">
@@ -41296,27 +41296,27 @@
       <c r="AT352" t="inlineStr"/>
       <c r="AW352" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX352" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY352" t="inlineStr"/>
       <c r="AZ352" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124629179</t>
+          <t>https://artportalen.se/Sighting/127784860</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="n">
-        <v>104914262</v>
+        <v>124629179</v>
       </c>
       <c r="B353" t="n">
-        <v>5199</v>
+        <v>58636</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -41324,16 +41324,16 @@
         </is>
       </c>
       <c r="E353" t="n">
-        <v>105930</v>
+        <v>103044</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G353" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H353" t="inlineStr">
@@ -41343,24 +41343,26 @@
       </c>
       <c r="I353" t="inlineStr"/>
       <c r="K353" t="inlineStr"/>
+      <c r="L353" t="inlineStr"/>
       <c r="M353" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N353" t="inlineStr"/>
       <c r="P353" t="inlineStr">
         <is>
-          <t>Leksand, Dlr</t>
+          <t>Moberg, Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q353" t="n">
-        <v>511544</v>
+        <v>511558</v>
       </c>
       <c r="R353" t="n">
-        <v>6733166</v>
+        <v>6733323</v>
       </c>
       <c r="S353" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T353" t="inlineStr">
         <is>
@@ -41384,22 +41386,27 @@
       </c>
       <c r="Y353" t="inlineStr">
         <is>
-          <t>2022-12-04</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="Z353" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA353" t="inlineStr">
         <is>
-          <t>2022-12-04</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="AB353" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>17:02</t>
+        </is>
+      </c>
+      <c r="AC353" t="inlineStr">
+        <is>
+          <t>Bofink Koltrast</t>
         </is>
       </c>
       <c r="AD353" t="b">
@@ -41414,24 +41421,24 @@
       <c r="AT353" t="inlineStr"/>
       <c r="AW353" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX353" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY353" t="inlineStr"/>
       <c r="AZ353" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104914262</t>
+          <t>https://artportalen.se/Sighting/124629179</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="n">
-        <v>109573919</v>
+        <v>104914262</v>
       </c>
       <c r="B354" t="n">
         <v>5199</v>
@@ -41460,25 +41467,22 @@
         </is>
       </c>
       <c r="I354" t="inlineStr"/>
-      <c r="J354" t="inlineStr"/>
       <c r="K354" t="inlineStr"/>
-      <c r="L354" t="inlineStr"/>
       <c r="M354" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N354" t="inlineStr"/>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P354" t="inlineStr">
         <is>
-          <t>Sjös-Moberg, Dlr</t>
+          <t>Leksand, Dlr</t>
         </is>
       </c>
       <c r="Q354" t="n">
-        <v>511560</v>
+        <v>511544</v>
       </c>
       <c r="R354" t="n">
-        <v>6733173</v>
+        <v>6733166</v>
       </c>
       <c r="S354" t="n">
         <v>25</v>
@@ -41505,27 +41509,22 @@
       </c>
       <c r="Y354" t="inlineStr">
         <is>
-          <t>2023-05-28</t>
+          <t>2022-12-04</t>
         </is>
       </c>
       <c r="Z354" t="inlineStr">
         <is>
-          <t>06:06</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA354" t="inlineStr">
         <is>
-          <t>2023-05-28</t>
+          <t>2022-12-04</t>
         </is>
       </c>
       <c r="AB354" t="inlineStr">
         <is>
-          <t>06:06</t>
-        </is>
-      </c>
-      <c r="AC354" t="inlineStr">
-        <is>
-          <t>Kan vara Bronshjon ?</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD354" t="b">
@@ -41534,31 +41533,30 @@
       <c r="AE354" t="b">
         <v>0</v>
       </c>
-      <c r="AF354" t="inlineStr"/>
       <c r="AG354" t="b">
         <v>0</v>
       </c>
       <c r="AT354" t="inlineStr"/>
       <c r="AW354" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX354" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY354" t="inlineStr"/>
       <c r="AZ354" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/109573919</t>
+          <t>https://artportalen.se/Sighting/104914262</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="n">
-        <v>127209685</v>
+        <v>109573919</v>
       </c>
       <c r="B355" t="n">
         <v>5199</v>
@@ -41592,23 +41590,23 @@
       <c r="L355" t="inlineStr"/>
       <c r="M355" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N355" t="inlineStr"/>
       <c r="P355" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Sjös-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q355" t="n">
-        <v>511253</v>
+        <v>511560</v>
       </c>
       <c r="R355" t="n">
-        <v>6733209</v>
+        <v>6733173</v>
       </c>
       <c r="S355" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T355" t="inlineStr">
         <is>
@@ -41632,22 +41630,27 @@
       </c>
       <c r="Y355" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2023-05-28</t>
         </is>
       </c>
       <c r="Z355" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>06:06</t>
         </is>
       </c>
       <c r="AA355" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2023-05-28</t>
         </is>
       </c>
       <c r="AB355" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>06:06</t>
+        </is>
+      </c>
+      <c r="AC355" t="inlineStr">
+        <is>
+          <t>Kan vara Bronshjon ?</t>
         </is>
       </c>
       <c r="AD355" t="b">
@@ -41674,13 +41677,13 @@
       <c r="AY355" t="inlineStr"/>
       <c r="AZ355" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127209685</t>
+          <t>https://artportalen.se/Sighting/109573919</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="n">
-        <v>127784849</v>
+        <v>127209685</v>
       </c>
       <c r="B356" t="n">
         <v>5199</v>
@@ -41709,21 +41712,25 @@
         </is>
       </c>
       <c r="I356" t="inlineStr"/>
+      <c r="J356" t="inlineStr"/>
+      <c r="K356" t="inlineStr"/>
+      <c r="L356" t="inlineStr"/>
       <c r="M356" t="inlineStr">
         <is>
           <t>äldre gnagspår</t>
         </is>
       </c>
+      <c r="N356" t="inlineStr"/>
       <c r="P356" t="inlineStr">
         <is>
-          <t>Sjös Moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q356" t="n">
-        <v>511697</v>
+        <v>511253</v>
       </c>
       <c r="R356" t="n">
-        <v>6733213</v>
+        <v>6733209</v>
       </c>
       <c r="S356" t="n">
         <v>10</v>
@@ -41750,12 +41757,22 @@
       </c>
       <c r="Y356" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="Z356" t="inlineStr">
+        <is>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA356" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AB356" t="inlineStr">
+        <is>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AD356" t="b">
@@ -41764,33 +41781,34 @@
       <c r="AE356" t="b">
         <v>0</v>
       </c>
+      <c r="AF356" t="inlineStr"/>
       <c r="AG356" t="b">
         <v>0</v>
       </c>
       <c r="AT356" t="inlineStr"/>
       <c r="AW356" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX356" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY356" t="inlineStr"/>
       <c r="AZ356" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127784849</t>
+          <t>https://artportalen.se/Sighting/127209685</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="n">
-        <v>104755491</v>
+        <v>127784849</v>
       </c>
       <c r="B357" t="n">
-        <v>8455</v>
+        <v>5199</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -41798,38 +41816,42 @@
         </is>
       </c>
       <c r="E357" t="n">
-        <v>106545</v>
+        <v>105930</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G357" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H357" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I357" t="inlineStr"/>
-      <c r="K357" t="inlineStr"/>
+      <c r="M357" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P357" t="inlineStr">
         <is>
-          <t>Leksand, Dlr</t>
+          <t>Sjös Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q357" t="n">
-        <v>511449</v>
+        <v>511697</v>
       </c>
       <c r="R357" t="n">
-        <v>6733313</v>
+        <v>6733213</v>
       </c>
       <c r="S357" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T357" t="inlineStr">
         <is>
@@ -41853,29 +41875,19 @@
       </c>
       <c r="Y357" t="inlineStr">
         <is>
-          <t>2022-11-20</t>
-        </is>
-      </c>
-      <c r="Z357" t="inlineStr">
-        <is>
-          <t>11:33</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="AA357" t="inlineStr">
         <is>
-          <t>2022-11-20</t>
-        </is>
-      </c>
-      <c r="AB357" t="inlineStr">
-        <is>
-          <t>11:33</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="AD357" t="b">
         <v>0</v>
       </c>
       <c r="AE357" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG357" t="b">
         <v>0</v>
@@ -41883,24 +41895,24 @@
       <c r="AT357" t="inlineStr"/>
       <c r="AW357" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX357" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson, Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY357" t="inlineStr"/>
       <c r="AZ357" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104755491</t>
+          <t>https://artportalen.se/Sighting/127784849</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="n">
-        <v>104776715</v>
+        <v>104755491</v>
       </c>
       <c r="B358" t="n">
         <v>8455</v>
@@ -41929,28 +41941,20 @@
         </is>
       </c>
       <c r="I358" t="inlineStr"/>
-      <c r="J358" t="inlineStr"/>
       <c r="K358" t="inlineStr"/>
-      <c r="L358" t="inlineStr"/>
-      <c r="M358" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N358" t="inlineStr"/>
       <c r="P358" t="inlineStr">
         <is>
-          <t>Moberget, Dlr</t>
+          <t>Leksand, Dlr</t>
         </is>
       </c>
       <c r="Q358" t="n">
-        <v>511498</v>
+        <v>511449</v>
       </c>
       <c r="R358" t="n">
-        <v>6733322</v>
+        <v>6733313</v>
       </c>
       <c r="S358" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T358" t="inlineStr">
         <is>
@@ -41977,47 +41981,51 @@
           <t>2022-11-20</t>
         </is>
       </c>
+      <c r="Z358" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
       <c r="AA358" t="inlineStr">
         <is>
           <t>2022-11-20</t>
         </is>
       </c>
-      <c r="AC358" t="inlineStr">
-        <is>
-          <t>Två gamla döda tallar (en låg och en stående)</t>
+      <c r="AB358" t="inlineStr">
+        <is>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD358" t="b">
         <v>0</v>
       </c>
       <c r="AE358" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF358" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG358" t="b">
         <v>0</v>
       </c>
       <c r="AT358" t="inlineStr"/>
       <c r="AW358" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX358" t="inlineStr">
         <is>
-          <t>Bo karlstens, Göran Ehn, Lisa Olson, Anna-Britt Olsson, Evalena Sköld</t>
+          <t>Anna-Britt Olsson, Bo karlstens</t>
         </is>
       </c>
       <c r="AY358" t="inlineStr"/>
       <c r="AZ358" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104776715</t>
+          <t>https://artportalen.se/Sighting/104755491</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="n">
-        <v>107243503</v>
+        <v>104776715</v>
       </c>
       <c r="B359" t="n">
         <v>8455</v>
@@ -42046,16 +42054,25 @@
         </is>
       </c>
       <c r="I359" t="inlineStr"/>
+      <c r="J359" t="inlineStr"/>
+      <c r="K359" t="inlineStr"/>
+      <c r="L359" t="inlineStr"/>
+      <c r="M359" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N359" t="inlineStr"/>
       <c r="P359" t="inlineStr">
         <is>
-          <t>Morberg, Dlr</t>
+          <t>Moberget, Dlr</t>
         </is>
       </c>
       <c r="Q359" t="n">
-        <v>511442</v>
+        <v>511498</v>
       </c>
       <c r="R359" t="n">
-        <v>6733305</v>
+        <v>6733322</v>
       </c>
       <c r="S359" t="n">
         <v>10</v>
@@ -42082,12 +42099,17 @@
       </c>
       <c r="Y359" t="inlineStr">
         <is>
-          <t>2022-11-21</t>
+          <t>2022-11-20</t>
         </is>
       </c>
       <c r="AA359" t="inlineStr">
         <is>
-          <t>2022-11-21</t>
+          <t>2022-11-20</t>
+        </is>
+      </c>
+      <c r="AC359" t="inlineStr">
+        <is>
+          <t>Två gamla döda tallar (en låg och en stående)</t>
         </is>
       </c>
       <c r="AD359" t="b">
@@ -42096,30 +42118,31 @@
       <c r="AE359" t="b">
         <v>0</v>
       </c>
+      <c r="AF359" t="inlineStr"/>
       <c r="AG359" t="b">
         <v>0</v>
       </c>
       <c r="AT359" t="inlineStr"/>
       <c r="AW359" t="inlineStr">
         <is>
-          <t>Jakob Wallin</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX359" t="inlineStr">
         <is>
-          <t>Jakob Wallin, Matilda Elgerud</t>
+          <t>Bo karlstens, Göran Ehn, Lisa Olson, Anna-Britt Olsson, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY359" t="inlineStr"/>
       <c r="AZ359" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/107243503</t>
+          <t>https://artportalen.se/Sighting/104776715</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="n">
-        <v>110255587</v>
+        <v>107243503</v>
       </c>
       <c r="B360" t="n">
         <v>8455</v>
@@ -42148,20 +42171,19 @@
         </is>
       </c>
       <c r="I360" t="inlineStr"/>
-      <c r="K360" t="inlineStr"/>
       <c r="P360" t="inlineStr">
         <is>
-          <t>Grim-Moberg, Dlr</t>
+          <t>Morberg, Dlr</t>
         </is>
       </c>
       <c r="Q360" t="n">
-        <v>511224</v>
+        <v>511442</v>
       </c>
       <c r="R360" t="n">
-        <v>6733170</v>
+        <v>6733305</v>
       </c>
       <c r="S360" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T360" t="inlineStr">
         <is>
@@ -42185,22 +42207,12 @@
       </c>
       <c r="Y360" t="inlineStr">
         <is>
-          <t>2023-06-21</t>
-        </is>
-      </c>
-      <c r="Z360" t="inlineStr">
-        <is>
-          <t>11:37</t>
+          <t>2022-11-21</t>
         </is>
       </c>
       <c r="AA360" t="inlineStr">
         <is>
-          <t>2023-06-21</t>
-        </is>
-      </c>
-      <c r="AB360" t="inlineStr">
-        <is>
-          <t>11:37</t>
+          <t>2022-11-21</t>
         </is>
       </c>
       <c r="AD360" t="b">
@@ -42215,77 +42227,66 @@
       <c r="AT360" t="inlineStr"/>
       <c r="AW360" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Jakob Wallin</t>
         </is>
       </c>
       <c r="AX360" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Jakob Wallin, Matilda Elgerud</t>
         </is>
       </c>
       <c r="AY360" t="inlineStr"/>
       <c r="AZ360" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110255587</t>
+          <t>https://artportalen.se/Sighting/107243503</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="n">
-        <v>123767910</v>
+        <v>110255587</v>
       </c>
       <c r="B361" t="n">
-        <v>56522</v>
+        <v>8455</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E361" t="n">
-        <v>206004</v>
+        <v>106545</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G361" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H361" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I361" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I361" t="inlineStr"/>
       <c r="K361" t="inlineStr"/>
-      <c r="L361" t="inlineStr"/>
-      <c r="M361" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N361" t="inlineStr"/>
       <c r="P361" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Grim-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q361" t="n">
-        <v>511475</v>
+        <v>511224</v>
       </c>
       <c r="R361" t="n">
-        <v>6733275</v>
+        <v>6733170</v>
       </c>
       <c r="S361" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T361" t="inlineStr">
         <is>
@@ -42309,27 +42310,22 @@
       </c>
       <c r="Y361" t="inlineStr">
         <is>
-          <t>2025-03-21</t>
+          <t>2023-06-21</t>
         </is>
       </c>
       <c r="Z361" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA361" t="inlineStr">
         <is>
-          <t>2025-03-21</t>
+          <t>2023-06-21</t>
         </is>
       </c>
       <c r="AB361" t="inlineStr">
         <is>
-          <t>10:13</t>
-        </is>
-      </c>
-      <c r="AC361" t="inlineStr">
-        <is>
-          <t>Den här dagen hade vi en tjäderexpert med oss.  Nu när inte längre Sjös Moberg har något skydd mot avverkning lägger jag ut alla tidigare dolda fynd som bara SKS har kunnat se. Om skogen faller ska alla veta vilka naturvärden som fanns.</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD361" t="b">
@@ -42349,19 +42345,19 @@
       </c>
       <c r="AX361" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY361" t="inlineStr"/>
       <c r="AZ361" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123767910</t>
+          <t>https://artportalen.se/Sighting/110255587</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="n">
-        <v>123767921</v>
+        <v>123767910</v>
       </c>
       <c r="B362" t="n">
         <v>56522</v>
@@ -42391,14 +42387,14 @@
       </c>
       <c r="I362" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K362" t="inlineStr"/>
       <c r="L362" t="inlineStr"/>
       <c r="M362" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N362" t="inlineStr"/>
@@ -42408,10 +42404,10 @@
         </is>
       </c>
       <c r="Q362" t="n">
-        <v>511660</v>
+        <v>511475</v>
       </c>
       <c r="R362" t="n">
-        <v>6733262</v>
+        <v>6733275</v>
       </c>
       <c r="S362" t="n">
         <v>15</v>
@@ -42443,7 +42439,7 @@
       </c>
       <c r="Z362" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA362" t="inlineStr">
@@ -42453,12 +42449,12 @@
       </c>
       <c r="AB362" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AC362" t="inlineStr">
         <is>
-          <t>Vid en liten tjärn, ett eller blöthål i en myr. 2944-2946</t>
+          <t>Den här dagen hade vi en tjäderexpert med oss.  Nu när inte längre Sjös Moberg har något skydd mot avverkning lägger jag ut alla tidigare dolda fynd som bara SKS har kunnat se. Om skogen faller ska alla veta vilka naturvärden som fanns.</t>
         </is>
       </c>
       <c r="AD362" t="b">
@@ -42484,13 +42480,13 @@
       <c r="AY362" t="inlineStr"/>
       <c r="AZ362" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123767921</t>
+          <t>https://artportalen.se/Sighting/123767910</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="n">
-        <v>123767922</v>
+        <v>123767921</v>
       </c>
       <c r="B363" t="n">
         <v>56522</v>
@@ -42520,7 +42516,7 @@
       </c>
       <c r="I363" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K363" t="inlineStr"/>
@@ -42537,10 +42533,10 @@
         </is>
       </c>
       <c r="Q363" t="n">
-        <v>511509</v>
+        <v>511660</v>
       </c>
       <c r="R363" t="n">
-        <v>6733246</v>
+        <v>6733262</v>
       </c>
       <c r="S363" t="n">
         <v>15</v>
@@ -42572,7 +42568,7 @@
       </c>
       <c r="Z363" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AA363" t="inlineStr">
@@ -42582,12 +42578,12 @@
       </c>
       <c r="AB363" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AC363" t="inlineStr">
         <is>
-          <t>2992</t>
+          <t>Vid en liten tjärn, ett eller blöthål i en myr. 2944-2946</t>
         </is>
       </c>
       <c r="AD363" t="b">
@@ -42613,13 +42609,13 @@
       <c r="AY363" t="inlineStr"/>
       <c r="AZ363" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123767922</t>
+          <t>https://artportalen.se/Sighting/123767921</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="n">
-        <v>123789075</v>
+        <v>123767922</v>
       </c>
       <c r="B364" t="n">
         <v>56522</v>
@@ -42654,7 +42650,11 @@
       </c>
       <c r="K364" t="inlineStr"/>
       <c r="L364" t="inlineStr"/>
-      <c r="M364" t="inlineStr"/>
+      <c r="M364" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N364" t="inlineStr"/>
       <c r="P364" t="inlineStr">
         <is>
@@ -42662,13 +42662,13 @@
         </is>
       </c>
       <c r="Q364" t="n">
-        <v>511660</v>
+        <v>511509</v>
       </c>
       <c r="R364" t="n">
-        <v>6733362</v>
+        <v>6733246</v>
       </c>
       <c r="S364" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T364" t="inlineStr">
         <is>
@@ -42697,7 +42697,7 @@
       </c>
       <c r="Z364" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA364" t="inlineStr">
@@ -42707,12 +42707,12 @@
       </c>
       <c r="AB364" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AC364" t="inlineStr">
         <is>
-          <t>6 kulor av äldre spillning</t>
+          <t>2992</t>
         </is>
       </c>
       <c r="AD364" t="b">
@@ -42738,13 +42738,13 @@
       <c r="AY364" t="inlineStr"/>
       <c r="AZ364" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123789075</t>
+          <t>https://artportalen.se/Sighting/123767922</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="n">
-        <v>126688587</v>
+        <v>123789075</v>
       </c>
       <c r="B365" t="n">
         <v>56522</v>
@@ -42772,24 +42772,28 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I365" t="inlineStr"/>
+      <c r="I365" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="K365" t="inlineStr"/>
       <c r="L365" t="inlineStr"/>
       <c r="M365" t="inlineStr"/>
       <c r="N365" t="inlineStr"/>
       <c r="P365" t="inlineStr">
         <is>
-          <t>Grim Moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q365" t="n">
-        <v>511380</v>
+        <v>511660</v>
       </c>
       <c r="R365" t="n">
-        <v>6733182</v>
+        <v>6733362</v>
       </c>
       <c r="S365" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T365" t="inlineStr">
         <is>
@@ -42813,27 +42817,27 @@
       </c>
       <c r="Y365" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="Z365" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA365" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="AB365" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AC365" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>6 kulor av äldre spillning</t>
         </is>
       </c>
       <c r="AD365" t="b">
@@ -42853,39 +42857,39 @@
       </c>
       <c r="AX365" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY365" t="inlineStr"/>
       <c r="AZ365" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126688587</t>
+          <t>https://artportalen.se/Sighting/123789075</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="n">
-        <v>110428414</v>
+        <v>126688587</v>
       </c>
       <c r="B366" t="n">
-        <v>58817</v>
+        <v>56522</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E366" t="n">
-        <v>208249</v>
+        <v>206004</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G366" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H366" t="inlineStr">
@@ -42893,33 +42897,24 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I366" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J366" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
+      <c r="I366" t="inlineStr"/>
       <c r="K366" t="inlineStr"/>
       <c r="L366" t="inlineStr"/>
       <c r="M366" t="inlineStr"/>
       <c r="N366" t="inlineStr"/>
       <c r="P366" t="inlineStr">
         <is>
-          <t>Stor-Moberg, Dlr</t>
+          <t>Grim Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q366" t="n">
-        <v>511549</v>
+        <v>511380</v>
       </c>
       <c r="R366" t="n">
-        <v>6733377</v>
+        <v>6733182</v>
       </c>
       <c r="S366" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T366" t="inlineStr">
         <is>
@@ -42943,27 +42938,27 @@
       </c>
       <c r="Y366" t="inlineStr">
         <is>
-          <t>2023-06-21</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="Z366" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA366" t="inlineStr">
         <is>
-          <t>2023-06-21</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AB366" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AC366" t="inlineStr">
         <is>
-          <t>Avverkningshotad fäbodskog, Höghöjd med mycket vitmossor, garnlav m.m.   Grodan var liten, ljusbrun med mörkare fläckar på ryggen och den försvann så snabbt i blåbärsriset att jag inte han ta något foto.</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD366" t="b">
@@ -42972,7 +42967,6 @@
       <c r="AE366" t="b">
         <v>0</v>
       </c>
-      <c r="AF366" t="inlineStr"/>
       <c r="AG366" t="b">
         <v>0</v>
       </c>
@@ -42990,13 +42984,13 @@
       <c r="AY366" t="inlineStr"/>
       <c r="AZ366" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110428414</t>
+          <t>https://artportalen.se/Sighting/126688587</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="n">
-        <v>124643526</v>
+        <v>110428414</v>
       </c>
       <c r="B367" t="n">
         <v>58817</v>
@@ -43026,12 +43020,12 @@
       </c>
       <c r="I367" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J367" t="inlineStr">
         <is>
-          <t>äggklumpar</t>
+          <t>ex.</t>
         </is>
       </c>
       <c r="K367" t="inlineStr"/>
@@ -43040,14 +43034,14 @@
       <c r="N367" t="inlineStr"/>
       <c r="P367" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Stor-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q367" t="n">
-        <v>511356</v>
+        <v>511549</v>
       </c>
       <c r="R367" t="n">
-        <v>6733152</v>
+        <v>6733377</v>
       </c>
       <c r="S367" t="n">
         <v>25</v>
@@ -43074,27 +43068,27 @@
       </c>
       <c r="Y367" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2023-06-21</t>
         </is>
       </c>
       <c r="Z367" t="inlineStr">
         <is>
-          <t>21:38</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA367" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2023-06-21</t>
         </is>
       </c>
       <c r="AB367" t="inlineStr">
         <is>
-          <t>21:38</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AC367" t="inlineStr">
         <is>
-          <t>Tre stora klumpar med grodrom låg i en vattenfylld  körskada efter den gamla fornvägen. Svårt att säga hur många grodyngel det var men sannolikt minst 1000. Kontinuitetsskog, hög luftfuktighet. Uppskattat antal. Så det lär bli många grodor i området. Midsommarafton 2023 såg jag grodor, 100-200 meter närmare fäboden till.</t>
+          <t>Avverkningshotad fäbodskog, Höghöjd med mycket vitmossor, garnlav m.m.   Grodan var liten, ljusbrun med mörkare fläckar på ryggen och den försvann så snabbt i blåbärsriset att jag inte han ta något foto.</t>
         </is>
       </c>
       <c r="AD367" t="b">
@@ -43115,22 +43109,22 @@
       </c>
       <c r="AX367" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY367" t="inlineStr"/>
       <c r="AZ367" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124643526</t>
+          <t>https://artportalen.se/Sighting/110428414</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="n">
-        <v>126258662</v>
+        <v>124643526</v>
       </c>
       <c r="B368" t="n">
-        <v>99035</v>
+        <v>58817</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -43138,49 +43132,50 @@
         </is>
       </c>
       <c r="E368" t="n">
-        <v>219790</v>
+        <v>208249</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G368" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H368" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I368" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="J368" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>äggklumpar</t>
         </is>
       </c>
       <c r="K368" t="inlineStr"/>
       <c r="L368" t="inlineStr"/>
+      <c r="M368" t="inlineStr"/>
       <c r="N368" t="inlineStr"/>
       <c r="P368" t="inlineStr">
         <is>
-          <t>MOBERG , Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q368" t="n">
-        <v>511330</v>
+        <v>511356</v>
       </c>
       <c r="R368" t="n">
-        <v>6733133</v>
+        <v>6733152</v>
       </c>
       <c r="S368" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T368" t="inlineStr">
         <is>
@@ -43204,27 +43199,27 @@
       </c>
       <c r="Y368" t="inlineStr">
         <is>
-          <t>2023-06-19</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="Z368" t="inlineStr">
         <is>
-          <t>21:15</t>
+          <t>21:38</t>
         </is>
       </c>
       <c r="AA368" t="inlineStr">
         <is>
-          <t>2023-06-19</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="AB368" t="inlineStr">
         <is>
-          <t>21:15</t>
+          <t>21:38</t>
         </is>
       </c>
       <c r="AC368" t="inlineStr">
         <is>
-          <t>KÄRRVIOLER, MM</t>
+          <t>Tre stora klumpar med grodrom låg i en vattenfylld  körskada efter den gamla fornvägen. Svårt att säga hur många grodyngel det var men sannolikt minst 1000. Kontinuitetsskog, hög luftfuktighet. Uppskattat antal. Så det lär bli många grodor i området. Midsommarafton 2023 såg jag grodor, 100-200 meter närmare fäboden till.</t>
         </is>
       </c>
       <c r="AD368" t="b">
@@ -43245,22 +43240,22 @@
       </c>
       <c r="AX368" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY368" t="inlineStr"/>
       <c r="AZ368" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126258662</t>
+          <t>https://artportalen.se/Sighting/124643526</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="n">
-        <v>104744866</v>
+        <v>126258662</v>
       </c>
       <c r="B369" t="n">
-        <v>99153</v>
+        <v>99035</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -43268,38 +43263,49 @@
         </is>
       </c>
       <c r="E369" t="n">
-        <v>219874</v>
+        <v>219790</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G369" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H369" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I369" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I369" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J369" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K369" t="inlineStr"/>
+      <c r="L369" t="inlineStr"/>
+      <c r="N369" t="inlineStr"/>
       <c r="P369" t="inlineStr">
         <is>
-          <t>Leksand, Dlr</t>
+          <t>MOBERG , Dlr</t>
         </is>
       </c>
       <c r="Q369" t="n">
-        <v>511495</v>
+        <v>511330</v>
       </c>
       <c r="R369" t="n">
-        <v>6733158</v>
+        <v>6733133</v>
       </c>
       <c r="S369" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T369" t="inlineStr">
         <is>
@@ -43323,30 +43329,36 @@
       </c>
       <c r="Y369" t="inlineStr">
         <is>
-          <t>2022-11-19</t>
+          <t>2023-06-19</t>
         </is>
       </c>
       <c r="Z369" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>21:15</t>
         </is>
       </c>
       <c r="AA369" t="inlineStr">
         <is>
-          <t>2022-11-19</t>
+          <t>2023-06-19</t>
         </is>
       </c>
       <c r="AB369" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>21:15</t>
+        </is>
+      </c>
+      <c r="AC369" t="inlineStr">
+        <is>
+          <t>KÄRRVIOLER, MM</t>
         </is>
       </c>
       <c r="AD369" t="b">
         <v>0</v>
       </c>
       <c r="AE369" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF369" t="inlineStr"/>
       <c r="AG369" t="b">
         <v>0</v>
       </c>
@@ -43364,52 +43376,52 @@
       <c r="AY369" t="inlineStr"/>
       <c r="AZ369" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104744866</t>
+          <t>https://artportalen.se/Sighting/126258662</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="n">
-        <v>111783083</v>
+        <v>104744866</v>
       </c>
       <c r="B370" t="n">
-        <v>99118</v>
+        <v>99153</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E370" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G370" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H370" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I370" t="inlineStr"/>
       <c r="K370" t="inlineStr"/>
       <c r="P370" t="inlineStr">
         <is>
-          <t>Grim-Moberg, Dlr</t>
+          <t>Leksand, Dlr</t>
         </is>
       </c>
       <c r="Q370" t="n">
-        <v>511377</v>
+        <v>511495</v>
       </c>
       <c r="R370" t="n">
-        <v>6733130</v>
+        <v>6733158</v>
       </c>
       <c r="S370" t="n">
         <v>25</v>
@@ -43436,19 +43448,29 @@
       </c>
       <c r="Y370" t="inlineStr">
         <is>
-          <t>2023-08-29</t>
+          <t>2022-11-19</t>
+        </is>
+      </c>
+      <c r="Z370" t="inlineStr">
+        <is>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA370" t="inlineStr">
         <is>
-          <t>2023-08-29</t>
+          <t>2022-11-19</t>
+        </is>
+      </c>
+      <c r="AB370" t="inlineStr">
+        <is>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD370" t="b">
         <v>0</v>
       </c>
       <c r="AE370" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG370" t="b">
         <v>0</v>
@@ -43456,24 +43478,24 @@
       <c r="AT370" t="inlineStr"/>
       <c r="AW370" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX370" t="inlineStr">
         <is>
-          <t>Göran Ehn, Bo karlstens, Kajsa Larsson, Lars-Erik Nilsson, Erik Danielsson, Lisa Olson</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY370" t="inlineStr"/>
       <c r="AZ370" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111783083</t>
+          <t>https://artportalen.se/Sighting/104744866</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="n">
-        <v>111783209</v>
+        <v>111783083</v>
       </c>
       <c r="B371" t="n">
         <v>99118</v>
@@ -43505,14 +43527,14 @@
       <c r="K371" t="inlineStr"/>
       <c r="P371" t="inlineStr">
         <is>
-          <t>Grim-Moberg, Grim-Moberg, Dlr</t>
+          <t>Grim-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q371" t="n">
-        <v>511280</v>
+        <v>511377</v>
       </c>
       <c r="R371" t="n">
-        <v>6733135</v>
+        <v>6733130</v>
       </c>
       <c r="S371" t="n">
         <v>25</v>
@@ -43542,19 +43564,9 @@
           <t>2023-08-29</t>
         </is>
       </c>
-      <c r="Z371" t="inlineStr">
-        <is>
-          <t>14:16</t>
-        </is>
-      </c>
       <c r="AA371" t="inlineStr">
         <is>
           <t>2023-08-29</t>
-        </is>
-      </c>
-      <c r="AB371" t="inlineStr">
-        <is>
-          <t>14:16</t>
         </is>
       </c>
       <c r="AD371" t="b">
@@ -43580,13 +43592,13 @@
       <c r="AY371" t="inlineStr"/>
       <c r="AZ371" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111783209</t>
+          <t>https://artportalen.se/Sighting/111783083</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="n">
-        <v>127029778</v>
+        <v>111783209</v>
       </c>
       <c r="B372" t="n">
         <v>99118</v>
@@ -43614,29 +43626,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I372" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J372" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I372" t="inlineStr"/>
+      <c r="K372" t="inlineStr"/>
       <c r="P372" t="inlineStr">
         <is>
-          <t>Moberg, Moberg, Dlr</t>
+          <t>Grim-Moberg, Grim-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q372" t="n">
-        <v>511678</v>
+        <v>511280</v>
       </c>
       <c r="R372" t="n">
-        <v>6733332</v>
+        <v>6733135</v>
       </c>
       <c r="S372" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="T372" t="inlineStr">
         <is>
@@ -43660,27 +43664,22 @@
       </c>
       <c r="Y372" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2023-08-29</t>
         </is>
       </c>
       <c r="Z372" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA372" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2023-08-29</t>
         </is>
       </c>
       <c r="AB372" t="inlineStr">
         <is>
-          <t>14:27</t>
-        </is>
-      </c>
-      <c r="AC372" t="inlineStr">
-        <is>
-          <t>3 blomstängel</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD372" t="b">
@@ -43695,24 +43694,24 @@
       <c r="AT372" t="inlineStr"/>
       <c r="AW372" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX372" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn, Bo karlstens, Kajsa Larsson, Lars-Erik Nilsson, Erik Danielsson, Lisa Olson</t>
         </is>
       </c>
       <c r="AY372" t="inlineStr"/>
       <c r="AZ372" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127029778</t>
+          <t>https://artportalen.se/Sighting/111783209</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="n">
-        <v>127784893</v>
+        <v>127029778</v>
       </c>
       <c r="B373" t="n">
         <v>99118</v>
@@ -43742,7 +43741,7 @@
       </c>
       <c r="I373" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J373" t="inlineStr">
@@ -43752,17 +43751,17 @@
       </c>
       <c r="P373" t="inlineStr">
         <is>
-          <t>Grim Moberg, Dlr</t>
+          <t>Moberg, Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q373" t="n">
-        <v>511495</v>
+        <v>511678</v>
       </c>
       <c r="R373" t="n">
-        <v>6733367</v>
+        <v>6733332</v>
       </c>
       <c r="S373" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T373" t="inlineStr">
         <is>
@@ -43786,12 +43785,27 @@
       </c>
       <c r="Y373" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="Z373" t="inlineStr">
+        <is>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA373" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AB373" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AC373" t="inlineStr">
+        <is>
+          <t>3 blomstängel</t>
         </is>
       </c>
       <c r="AD373" t="b">
@@ -43806,24 +43820,24 @@
       <c r="AT373" t="inlineStr"/>
       <c r="AW373" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX373" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY373" t="inlineStr"/>
       <c r="AZ373" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127784893</t>
+          <t>https://artportalen.se/Sighting/127029778</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="n">
-        <v>127784894</v>
+        <v>127784893</v>
       </c>
       <c r="B374" t="n">
         <v>99118</v>
@@ -43853,7 +43867,7 @@
       </c>
       <c r="I374" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>500</t>
         </is>
       </c>
       <c r="J374" t="inlineStr">
@@ -43867,10 +43881,10 @@
         </is>
       </c>
       <c r="Q374" t="n">
-        <v>511559</v>
+        <v>511495</v>
       </c>
       <c r="R374" t="n">
-        <v>6733392</v>
+        <v>6733367</v>
       </c>
       <c r="S374" t="n">
         <v>10</v>
@@ -43928,13 +43942,13 @@
       <c r="AY374" t="inlineStr"/>
       <c r="AZ374" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127784894</t>
+          <t>https://artportalen.se/Sighting/127784893</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="n">
-        <v>127784987</v>
+        <v>127784894</v>
       </c>
       <c r="B375" t="n">
         <v>99118</v>
@@ -43964,7 +43978,7 @@
       </c>
       <c r="I375" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J375" t="inlineStr">
@@ -43972,21 +43986,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K375" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
       <c r="P375" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Grim Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q375" t="n">
-        <v>512101</v>
+        <v>511559</v>
       </c>
       <c r="R375" t="n">
-        <v>6733373</v>
+        <v>6733392</v>
       </c>
       <c r="S375" t="n">
         <v>10</v>
@@ -44021,11 +44030,6 @@
           <t>2025-08-24</t>
         </is>
       </c>
-      <c r="AC375" t="inlineStr">
-        <is>
-          <t>12 blomstjälkar</t>
-        </is>
-      </c>
       <c r="AD375" t="b">
         <v>0</v>
       </c>
@@ -44049,51 +44053,65 @@
       <c r="AY375" t="inlineStr"/>
       <c r="AZ375" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127784987</t>
+          <t>https://artportalen.se/Sighting/127784894</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="n">
-        <v>127013784</v>
+        <v>127784987</v>
       </c>
       <c r="B376" t="n">
-        <v>97983</v>
+        <v>99118</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E376" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G376" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H376" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I376" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I376" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="J376" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K376" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P376" t="inlineStr">
         <is>
-          <t>Stor Moberg norra, Stor Moberg norra, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q376" t="n">
-        <v>511594</v>
+        <v>512101</v>
       </c>
       <c r="R376" t="n">
-        <v>6733536</v>
+        <v>6733373</v>
       </c>
       <c r="S376" t="n">
         <v>10</v>
@@ -44120,22 +44138,17 @@
       </c>
       <c r="Y376" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="Z376" t="inlineStr">
-        <is>
-          <t>19:47</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="AA376" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AB376" t="inlineStr">
-        <is>
-          <t>19:47</t>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AC376" t="inlineStr">
+        <is>
+          <t>12 blomstjälkar</t>
         </is>
       </c>
       <c r="AD376" t="b">
@@ -44150,24 +44163,24 @@
       <c r="AT376" t="inlineStr"/>
       <c r="AW376" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX376" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY376" t="inlineStr"/>
       <c r="AZ376" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127013784</t>
+          <t>https://artportalen.se/Sighting/127784987</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="n">
-        <v>127085229</v>
+        <v>127013784</v>
       </c>
       <c r="B377" t="n">
         <v>97983</v>
@@ -44198,14 +44211,14 @@
       <c r="I377" t="inlineStr"/>
       <c r="P377" t="inlineStr">
         <is>
-          <t>Grim-Moberg, Dlr</t>
+          <t>Stor Moberg norra, Stor Moberg norra, Dlr</t>
         </is>
       </c>
       <c r="Q377" t="n">
-        <v>511627</v>
+        <v>511594</v>
       </c>
       <c r="R377" t="n">
-        <v>6733567</v>
+        <v>6733536</v>
       </c>
       <c r="S377" t="n">
         <v>10</v>
@@ -44232,12 +44245,22 @@
       </c>
       <c r="Y377" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="Z377" t="inlineStr">
+        <is>
+          <t>19:47</t>
         </is>
       </c>
       <c r="AA377" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AB377" t="inlineStr">
+        <is>
+          <t>19:47</t>
         </is>
       </c>
       <c r="AD377" t="b">
@@ -44252,24 +44275,24 @@
       <c r="AT377" t="inlineStr"/>
       <c r="AW377" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX377" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY377" t="inlineStr"/>
       <c r="AZ377" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127085229</t>
+          <t>https://artportalen.se/Sighting/127013784</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="n">
-        <v>127085230</v>
+        <v>127085229</v>
       </c>
       <c r="B378" t="n">
         <v>97983</v>
@@ -44304,10 +44327,10 @@
         </is>
       </c>
       <c r="Q378" t="n">
-        <v>511609</v>
+        <v>511627</v>
       </c>
       <c r="R378" t="n">
-        <v>6733537</v>
+        <v>6733567</v>
       </c>
       <c r="S378" t="n">
         <v>10</v>
@@ -44365,16 +44388,16 @@
       <c r="AY378" t="inlineStr"/>
       <c r="AZ378" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127085230</t>
+          <t>https://artportalen.se/Sighting/127085229</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="n">
-        <v>111966750</v>
+        <v>127085230</v>
       </c>
       <c r="B379" t="n">
-        <v>101326</v>
+        <v>97983</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -44382,38 +44405,37 @@
         </is>
       </c>
       <c r="E379" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G379" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H379" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I379" t="inlineStr"/>
-      <c r="K379" t="inlineStr"/>
       <c r="P379" t="inlineStr">
         <is>
-          <t>Stor-Moberg, Dlr</t>
+          <t>Grim-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q379" t="n">
-        <v>511474</v>
+        <v>511609</v>
       </c>
       <c r="R379" t="n">
-        <v>6733504</v>
+        <v>6733537</v>
       </c>
       <c r="S379" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T379" t="inlineStr">
         <is>
@@ -44437,22 +44459,12 @@
       </c>
       <c r="Y379" t="inlineStr">
         <is>
-          <t>2023-09-08</t>
-        </is>
-      </c>
-      <c r="Z379" t="inlineStr">
-        <is>
-          <t>17:52</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="AA379" t="inlineStr">
         <is>
-          <t>2023-09-08</t>
-        </is>
-      </c>
-      <c r="AB379" t="inlineStr">
-        <is>
-          <t>17:52</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="AD379" t="b">
@@ -44467,27 +44479,27 @@
       <c r="AT379" t="inlineStr"/>
       <c r="AW379" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX379" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY379" t="inlineStr"/>
       <c r="AZ379" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111966750</t>
+          <t>https://artportalen.se/Sighting/127085230</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="n">
-        <v>110253973</v>
+        <v>111966750</v>
       </c>
       <c r="B380" t="n">
-        <v>99038</v>
+        <v>101326</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -44495,35 +44507,35 @@
         </is>
       </c>
       <c r="E380" t="n">
-        <v>223597</v>
+        <v>222498</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G380" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H380" t="inlineStr"/>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H380" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
       <c r="I380" t="inlineStr"/>
-      <c r="K380" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K380" t="inlineStr"/>
       <c r="P380" t="inlineStr">
         <is>
-          <t>Grim-Moberg, Dlr</t>
+          <t>Stor-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q380" t="n">
-        <v>511224</v>
+        <v>511474</v>
       </c>
       <c r="R380" t="n">
-        <v>6733170</v>
+        <v>6733504</v>
       </c>
       <c r="S380" t="n">
         <v>25</v>
@@ -44550,22 +44562,22 @@
       </c>
       <c r="Y380" t="inlineStr">
         <is>
-          <t>2023-06-21</t>
+          <t>2023-09-08</t>
         </is>
       </c>
       <c r="Z380" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA380" t="inlineStr">
         <is>
-          <t>2023-06-21</t>
+          <t>2023-09-08</t>
         </is>
       </c>
       <c r="AB380" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AD380" t="b">
@@ -44591,16 +44603,16 @@
       <c r="AY380" t="inlineStr"/>
       <c r="AZ380" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110253973</t>
+          <t>https://artportalen.se/Sighting/111966750</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="n">
-        <v>134453125</v>
+        <v>110253973</v>
       </c>
       <c r="B381" t="n">
-        <v>99115</v>
+        <v>99038</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -44621,32 +44633,25 @@
         </is>
       </c>
       <c r="H381" t="inlineStr"/>
-      <c r="I381" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J381" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K381" t="inlineStr"/>
-      <c r="L381" t="inlineStr"/>
-      <c r="N381" t="inlineStr"/>
+      <c r="I381" t="inlineStr"/>
+      <c r="K381" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P381" t="inlineStr">
         <is>
-          <t>Grim-Moberg, Grim-Moberg, Dlr</t>
+          <t>Grim-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q381" t="n">
-        <v>511081</v>
+        <v>511224</v>
       </c>
       <c r="R381" t="n">
-        <v>6733295</v>
+        <v>6733170</v>
       </c>
       <c r="S381" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T381" t="inlineStr">
         <is>
@@ -44670,27 +44675,22 @@
       </c>
       <c r="Y381" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2023-06-21</t>
         </is>
       </c>
       <c r="Z381" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA381" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2023-06-21</t>
         </is>
       </c>
       <c r="AB381" t="inlineStr">
         <is>
-          <t>14:52</t>
-        </is>
-      </c>
-      <c r="AC381" t="inlineStr">
-        <is>
-          <t>Jag gick ca 200m mot norr efter kraftledningen och de två första stod i korsningen.</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD381" t="b">
@@ -44699,7 +44699,6 @@
       <c r="AE381" t="b">
         <v>0</v>
       </c>
-      <c r="AF381" t="inlineStr"/>
       <c r="AG381" t="b">
         <v>0</v>
       </c>
@@ -44717,65 +44716,62 @@
       <c r="AY381" t="inlineStr"/>
       <c r="AZ381" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134453125</t>
+          <t>https://artportalen.se/Sighting/110253973</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="n">
-        <v>127158796</v>
+        <v>134453125</v>
       </c>
       <c r="B382" t="n">
-        <v>92329</v>
+        <v>99115</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E382" t="n">
-        <v>6040186</v>
+        <v>223597</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G382" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
-        </is>
-      </c>
-      <c r="H382" t="inlineStr">
-        <is>
-          <t>(Pers.:Fr.) Quél.</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H382" t="inlineStr"/>
       <c r="I382" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J382" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K382" t="inlineStr"/>
+      <c r="L382" t="inlineStr"/>
       <c r="N382" t="inlineStr"/>
       <c r="P382" t="inlineStr">
         <is>
-          <t>Moberg, Dlr</t>
+          <t>Grim-Moberg, Grim-Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q382" t="n">
-        <v>511347</v>
+        <v>511081</v>
       </c>
       <c r="R382" t="n">
-        <v>6733129</v>
+        <v>6733295</v>
       </c>
       <c r="S382" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T382" t="inlineStr">
         <is>
@@ -44799,27 +44795,27 @@
       </c>
       <c r="Y382" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="Z382" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA382" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="AB382" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AC382" t="inlineStr">
         <is>
-          <t>På samma gran (död) som Thomsons trädgnagare</t>
+          <t>Jag gick ca 200m mot norr efter kraftledningen och de två första stod i korsningen.</t>
         </is>
       </c>
       <c r="AD382" t="b">
@@ -44835,24 +44831,24 @@
       <c r="AT382" t="inlineStr"/>
       <c r="AW382" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX382" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY382" t="inlineStr"/>
       <c r="AZ382" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127158796</t>
+          <t>https://artportalen.se/Sighting/134453125</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="n">
-        <v>127784892</v>
+        <v>127158796</v>
       </c>
       <c r="B383" t="n">
         <v>92329</v>
@@ -44880,17 +44876,28 @@
           <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
-      <c r="I383" t="inlineStr"/>
+      <c r="I383" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J383" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K383" t="inlineStr"/>
+      <c r="N383" t="inlineStr"/>
       <c r="P383" t="inlineStr">
         <is>
-          <t>Grim Moberg, Dlr</t>
+          <t>Moberg, Dlr</t>
         </is>
       </c>
       <c r="Q383" t="n">
-        <v>511479</v>
+        <v>511347</v>
       </c>
       <c r="R383" t="n">
-        <v>6733529</v>
+        <v>6733129</v>
       </c>
       <c r="S383" t="n">
         <v>10</v>
@@ -44917,12 +44924,27 @@
       </c>
       <c r="Y383" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="Z383" t="inlineStr">
+        <is>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA383" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AB383" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="AC383" t="inlineStr">
+        <is>
+          <t>På samma gran (död) som Thomsons trädgnagare</t>
         </is>
       </c>
       <c r="AD383" t="b">
@@ -44931,22 +44953,125 @@
       <c r="AE383" t="b">
         <v>0</v>
       </c>
+      <c r="AF383" t="inlineStr"/>
       <c r="AG383" t="b">
         <v>0</v>
       </c>
       <c r="AT383" t="inlineStr"/>
       <c r="AW383" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX383" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY383" t="inlineStr"/>
       <c r="AZ383" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127158796</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="n">
+        <v>127784892</v>
+      </c>
+      <c r="B384" t="n">
+        <v>92329</v>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E384" t="n">
+        <v>6040186</v>
+      </c>
+      <c r="F384" t="inlineStr">
+        <is>
+          <t>Kötticka</t>
+        </is>
+      </c>
+      <c r="G384" t="inlineStr">
+        <is>
+          <t>Leptoporus mollis</t>
+        </is>
+      </c>
+      <c r="H384" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I384" t="inlineStr"/>
+      <c r="P384" t="inlineStr">
+        <is>
+          <t>Grim Moberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q384" t="n">
+        <v>511479</v>
+      </c>
+      <c r="R384" t="n">
+        <v>6733529</v>
+      </c>
+      <c r="S384" t="n">
+        <v>10</v>
+      </c>
+      <c r="T384" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U384" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V384" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W384" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y384" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AA384" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AD384" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE384" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG384" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT384" t="inlineStr"/>
+      <c r="AW384" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX384" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY384" t="inlineStr"/>
+      <c r="AZ384" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/127784892</t>
         </is>
@@ -45336,6 +45461,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ381" r:id="rId380"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ382" r:id="rId381"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ383" r:id="rId382"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ384" r:id="rId383"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 1898-2025 artfynd.xlsx
+++ b/artfynd/S 1898-2025 artfynd.xlsx
@@ -1638,7 +1638,7 @@
         <v>127009893</v>
       </c>
       <c r="B11" t="n">
-        <v>89479</v>
+        <v>89485</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/S 1898-2025 artfynd.xlsx
+++ b/artfynd/S 1898-2025 artfynd.xlsx
@@ -1638,7 +1638,7 @@
         <v>127009893</v>
       </c>
       <c r="B11" t="n">
-        <v>89485</v>
+        <v>89489</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/S 1898-2025 artfynd.xlsx
+++ b/artfynd/S 1898-2025 artfynd.xlsx
@@ -1638,7 +1638,7 @@
         <v>127009893</v>
       </c>
       <c r="B11" t="n">
-        <v>89489</v>
+        <v>89491</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/S 1898-2025 artfynd.xlsx
+++ b/artfynd/S 1898-2025 artfynd.xlsx
@@ -1638,7 +1638,7 @@
         <v>127009893</v>
       </c>
       <c r="B11" t="n">
-        <v>89491</v>
+        <v>89504</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -34960,7 +34960,7 @@
         <v>137124272</v>
       </c>
       <c r="B299" t="n">
-        <v>57195</v>
+        <v>57208</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>

--- a/artfynd/S 1898-2025 artfynd.xlsx
+++ b/artfynd/S 1898-2025 artfynd.xlsx
@@ -1638,7 +1638,7 @@
         <v>127009893</v>
       </c>
       <c r="B11" t="n">
-        <v>89504</v>
+        <v>89506</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -34960,7 +34960,7 @@
         <v>137124272</v>
       </c>
       <c r="B299" t="n">
-        <v>57208</v>
+        <v>57210</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>

--- a/artfynd/S 1898-2025 artfynd.xlsx
+++ b/artfynd/S 1898-2025 artfynd.xlsx
@@ -1638,7 +1638,7 @@
         <v>127009893</v>
       </c>
       <c r="B11" t="n">
-        <v>89506</v>
+        <v>89509</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/S 1898-2025 artfynd.xlsx
+++ b/artfynd/S 1898-2025 artfynd.xlsx
@@ -1638,7 +1638,7 @@
         <v>127009893</v>
       </c>
       <c r="B11" t="n">
-        <v>89509</v>
+        <v>89519</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -34960,7 +34960,7 @@
         <v>137124272</v>
       </c>
       <c r="B299" t="n">
-        <v>57210</v>
+        <v>57220</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>

--- a/artfynd/S 1898-2025 artfynd.xlsx
+++ b/artfynd/S 1898-2025 artfynd.xlsx
@@ -1638,7 +1638,7 @@
         <v>127009893</v>
       </c>
       <c r="B11" t="n">
-        <v>89519</v>
+        <v>89520</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/S 1898-2025 artfynd.xlsx
+++ b/artfynd/S 1898-2025 artfynd.xlsx
@@ -1638,7 +1638,7 @@
         <v>127009893</v>
       </c>
       <c r="B11" t="n">
-        <v>89520</v>
+        <v>89523</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -34960,7 +34960,7 @@
         <v>137124272</v>
       </c>
       <c r="B299" t="n">
-        <v>57220</v>
+        <v>57221</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>

--- a/artfynd/S 1898-2025 artfynd.xlsx
+++ b/artfynd/S 1898-2025 artfynd.xlsx
@@ -1638,7 +1638,7 @@
         <v>127009893</v>
       </c>
       <c r="B11" t="n">
-        <v>89523</v>
+        <v>89528</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/S 1898-2025 artfynd.xlsx
+++ b/artfynd/S 1898-2025 artfynd.xlsx
@@ -1638,7 +1638,7 @@
         <v>127009893</v>
       </c>
       <c r="B11" t="n">
-        <v>89528</v>
+        <v>89539</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/S 1898-2025 artfynd.xlsx
+++ b/artfynd/S 1898-2025 artfynd.xlsx
@@ -1638,7 +1638,7 @@
         <v>127009893</v>
       </c>
       <c r="B11" t="n">
-        <v>89539</v>
+        <v>89540</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/S 1898-2025 artfynd.xlsx
+++ b/artfynd/S 1898-2025 artfynd.xlsx
@@ -1638,7 +1638,7 @@
         <v>127009893</v>
       </c>
       <c r="B11" t="n">
-        <v>89540</v>
+        <v>89543</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/S 1898-2025 artfynd.xlsx
+++ b/artfynd/S 1898-2025 artfynd.xlsx
@@ -1638,7 +1638,7 @@
         <v>127009893</v>
       </c>
       <c r="B11" t="n">
-        <v>89543</v>
+        <v>89544</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
